--- a/data/nv_aio_bc.xlsx
+++ b/data/nv_aio_bc.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I268"/>
+  <dimension ref="A1:I294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1307,23 +1307,23 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E26">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="F26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H26">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I26">
-        <v>120553703</v>
+        <v>409544443</v>
       </c>
     </row>
     <row r="27">
@@ -1339,28 +1339,28 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E27">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="F27">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I27">
-        <v>409544443</v>
+        <v>120553703</v>
       </c>
     </row>
     <row r="28">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1755,7 +1755,7 @@
         </is>
       </c>
       <c r="E38">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F38">
         <v>1</v>
@@ -1767,23 +1767,23 @@
         <v>0</v>
       </c>
       <c r="I38">
-        <v>21222222</v>
+        <v>42133333</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1798,13 +1798,13 @@
         <v>1</v>
       </c>
       <c r="G39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H39">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="I39">
-        <v>128800000</v>
+        <v>21222222</v>
       </c>
     </row>
     <row r="40">
@@ -1825,11 +1825,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Chờ ký PLHĐ</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E40">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F40">
         <v>1</v>
@@ -1838,10 +1838,10 @@
         <v>1</v>
       </c>
       <c r="H40">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="I40">
-        <v>131944444</v>
+        <v>128800000</v>
       </c>
     </row>
     <row r="41">
@@ -1862,23 +1862,23 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Chờ ký PLHĐ</t>
         </is>
       </c>
       <c r="E41">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="I41">
-        <v>87037036</v>
+        <v>131944444</v>
       </c>
     </row>
     <row r="42">
@@ -1899,23 +1899,23 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E42">
-        <v>86</v>
+        <v>19</v>
       </c>
       <c r="F42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H42">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="I42">
-        <v>499074074</v>
+        <v>87037036</v>
       </c>
     </row>
     <row r="43">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1936,11 +1936,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E43">
-        <v>7</v>
+        <v>86</v>
       </c>
       <c r="F43">
         <v>1</v>
@@ -1949,10 +1949,10 @@
         <v>1</v>
       </c>
       <c r="H43">
-        <v>7</v>
+        <v>86</v>
       </c>
       <c r="I43">
-        <v>12962962</v>
+        <v>499074074</v>
       </c>
     </row>
     <row r="44">
@@ -1973,11 +1973,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Chờ hàng TTQH</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E44">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F44">
         <v>1</v>
@@ -1986,10 +1986,10 @@
         <v>1</v>
       </c>
       <c r="H44">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I44">
-        <v>83888888</v>
+        <v>12962962</v>
       </c>
     </row>
     <row r="45">
@@ -2010,11 +2010,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Chờ ký PLHĐ</t>
+          <t>Chờ hàng TTQH</t>
         </is>
       </c>
       <c r="E45">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F45">
         <v>1</v>
@@ -2023,10 +2023,10 @@
         <v>1</v>
       </c>
       <c r="H45">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="I45">
-        <v>148037037</v>
+        <v>83888888</v>
       </c>
     </row>
     <row r="46">
@@ -2047,11 +2047,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Chờ ký PLHĐ</t>
         </is>
       </c>
       <c r="E46">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="F46">
         <v>1</v>
@@ -2060,10 +2060,10 @@
         <v>1</v>
       </c>
       <c r="H46">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="I46">
-        <v>62240740</v>
+        <v>148037037</v>
       </c>
     </row>
     <row r="47">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2084,23 +2084,23 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E47">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F47">
         <v>1</v>
       </c>
       <c r="G47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H47">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I47">
-        <v>13888888</v>
+        <v>62240740</v>
       </c>
     </row>
     <row r="48">
@@ -2111,7 +2111,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2121,23 +2121,23 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E48">
-        <v>156</v>
+        <v>7</v>
       </c>
       <c r="F48">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G48">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H48">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="I48">
-        <v>1025448236</v>
+        <v>13888888</v>
       </c>
     </row>
     <row r="49">
@@ -2158,23 +2158,23 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Chờ ký PLHĐ</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E49">
-        <v>17</v>
+        <v>156</v>
       </c>
       <c r="F49">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G49">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H49">
-        <v>17</v>
+        <v>156</v>
       </c>
       <c r="I49">
-        <v>139650000</v>
+        <v>1025448236</v>
       </c>
     </row>
     <row r="50">
@@ -2195,23 +2195,23 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Chờ ký PLHĐ</t>
         </is>
       </c>
       <c r="E50">
-        <v>124</v>
+        <v>17</v>
       </c>
       <c r="F50">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G50">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H50">
-        <v>70</v>
+        <v>17</v>
       </c>
       <c r="I50">
-        <v>1078973884</v>
+        <v>139650000</v>
       </c>
     </row>
     <row r="51">
@@ -2232,23 +2232,23 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Đã hoàn thành</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E51">
-        <v>36</v>
+        <v>124</v>
       </c>
       <c r="F51">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G51">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H51">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="I51">
-        <v>238175925</v>
+        <v>1078973884</v>
       </c>
     </row>
     <row r="52">
@@ -2264,16 +2264,16 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Đã hoàn thành</t>
         </is>
       </c>
       <c r="E52">
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="F52">
         <v>1</v>
@@ -2282,10 +2282,10 @@
         <v>1</v>
       </c>
       <c r="H52">
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="I52">
-        <v>178703703</v>
+        <v>238175925</v>
       </c>
     </row>
     <row r="53">
@@ -2296,33 +2296,33 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E53">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="F53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H53">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="I53">
-        <v>488888888</v>
+        <v>178703703</v>
       </c>
     </row>
     <row r="54">
@@ -2343,23 +2343,23 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E54">
-        <v>60</v>
+        <v>106</v>
       </c>
       <c r="F54">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G54">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H54">
-        <v>60</v>
+        <v>106</v>
       </c>
       <c r="I54">
-        <v>319814814</v>
+        <v>488888888</v>
       </c>
     </row>
     <row r="55">
@@ -2380,23 +2380,23 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Đã hoàn thành</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E55">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="F55">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G55">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H55">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="I55">
-        <v>50925925</v>
+        <v>319814814</v>
       </c>
     </row>
     <row r="56">
@@ -2407,7 +2407,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2417,23 +2417,23 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Đã hoàn thành</t>
         </is>
       </c>
       <c r="E56">
-        <v>280</v>
+        <v>10</v>
       </c>
       <c r="F56">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G56">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="H56">
-        <v>280</v>
+        <v>10</v>
       </c>
       <c r="I56">
-        <v>1923274762</v>
+        <v>50925925</v>
       </c>
     </row>
     <row r="57">
@@ -2454,23 +2454,23 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Chờ ký PLHĐ</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E57">
-        <v>26</v>
+        <v>280</v>
       </c>
       <c r="F57">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G57">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="H57">
-        <v>26</v>
+        <v>280</v>
       </c>
       <c r="I57">
-        <v>170370369</v>
+        <v>1923274762</v>
       </c>
     </row>
     <row r="58">
@@ -2491,23 +2491,23 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Chờ ký PLHĐ</t>
         </is>
       </c>
       <c r="E58">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F58">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G58">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H58">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="I58">
-        <v>188074073</v>
+        <v>170370369</v>
       </c>
     </row>
     <row r="59">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2528,23 +2528,23 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E59">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="F59">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G59">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H59">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="I59">
-        <v>287037035</v>
+        <v>188074073</v>
       </c>
     </row>
     <row r="60">
@@ -2565,23 +2565,23 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Chờ ký PLHĐ</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E60">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="F60">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G60">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H60">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="I60">
-        <v>44444444</v>
+        <v>287037035</v>
       </c>
     </row>
     <row r="61">
@@ -2602,23 +2602,23 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Chờ ký PLHĐ</t>
         </is>
       </c>
       <c r="E61">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="F61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H61">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="I61">
-        <v>109685184</v>
+        <v>44444444</v>
       </c>
     </row>
     <row r="62">
@@ -2629,7 +2629,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2639,23 +2639,23 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E62">
-        <v>132</v>
+        <v>46</v>
       </c>
       <c r="F62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H62">
-        <v>132</v>
+        <v>46</v>
       </c>
       <c r="I62">
-        <v>643554609</v>
+        <v>109685184</v>
       </c>
     </row>
     <row r="63">
@@ -2676,23 +2676,23 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Chờ ký PLHĐ</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E63">
-        <v>2</v>
+        <v>132</v>
       </c>
       <c r="F63">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G63">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H63">
-        <v>2</v>
+        <v>132</v>
       </c>
       <c r="I63">
-        <v>21296295</v>
+        <v>643554609</v>
       </c>
     </row>
     <row r="64">
@@ -2713,23 +2713,23 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Chờ ký PLHĐ</t>
         </is>
       </c>
       <c r="E64">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="F64">
+        <v>1</v>
+      </c>
+      <c r="G64">
+        <v>1</v>
+      </c>
+      <c r="H64">
         <v>2</v>
       </c>
-      <c r="G64">
-        <v>1</v>
-      </c>
-      <c r="H64">
-        <v>10</v>
-      </c>
       <c r="I64">
-        <v>167592592</v>
+        <v>21296295</v>
       </c>
     </row>
     <row r="65">
@@ -2750,23 +2750,23 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E65">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H65">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="I65">
-        <v>236609331</v>
+        <v>167592592</v>
       </c>
     </row>
     <row r="66">
@@ -2782,7 +2782,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2791,19 +2791,19 @@
         </is>
       </c>
       <c r="E66">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="F66">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G66">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H66">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="I66">
-        <v>11574074</v>
+        <v>236609331</v>
       </c>
     </row>
     <row r="67">
@@ -2814,21 +2814,21 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E67">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="F67">
         <v>1</v>
@@ -2837,10 +2837,10 @@
         <v>1</v>
       </c>
       <c r="H67">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="I67">
-        <v>127546296</v>
+        <v>11574074</v>
       </c>
     </row>
     <row r="68">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2865,19 +2865,19 @@
         </is>
       </c>
       <c r="E68">
-        <v>170</v>
+        <v>25</v>
       </c>
       <c r="F68">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G68">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H68">
-        <v>78</v>
+        <v>25</v>
       </c>
       <c r="I68">
-        <v>805485887</v>
+        <v>127546296</v>
       </c>
     </row>
     <row r="69">
@@ -2898,23 +2898,23 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E69">
-        <v>97</v>
+        <v>170</v>
       </c>
       <c r="F69">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G69">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H69">
-        <v>5</v>
+        <v>78</v>
       </c>
       <c r="I69">
-        <v>750386299</v>
+        <v>805485887</v>
       </c>
     </row>
     <row r="70">
@@ -2935,23 +2935,23 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E70">
-        <v>16</v>
+        <v>97</v>
       </c>
       <c r="F70">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G70">
         <v>1</v>
       </c>
       <c r="H70">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="I70">
-        <v>162744629</v>
+        <v>750386299</v>
       </c>
     </row>
     <row r="71">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2972,23 +2972,23 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E71">
-        <v>313</v>
+        <v>16</v>
       </c>
       <c r="F71">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G71">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H71">
-        <v>313</v>
+        <v>14</v>
       </c>
       <c r="I71">
-        <v>1662373413</v>
+        <v>162744629</v>
       </c>
     </row>
     <row r="72">
@@ -3009,23 +3009,23 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Chờ ký PLHĐ</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E72">
-        <v>22</v>
+        <v>313</v>
       </c>
       <c r="F72">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G72">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H72">
-        <v>22</v>
+        <v>313</v>
       </c>
       <c r="I72">
-        <v>171296296</v>
+        <v>1662373413</v>
       </c>
     </row>
     <row r="73">
@@ -3046,23 +3046,23 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Chờ ký PLHĐ</t>
         </is>
       </c>
       <c r="E73">
-        <v>295</v>
+        <v>22</v>
       </c>
       <c r="F73">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G73">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H73">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="I73">
-        <v>2030481726</v>
+        <v>171296296</v>
       </c>
     </row>
     <row r="74">
@@ -3083,23 +3083,23 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E74">
+        <v>295</v>
+      </c>
+      <c r="F74">
         <v>9</v>
       </c>
-      <c r="F74">
-        <v>1</v>
-      </c>
       <c r="G74">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H74">
-        <v>9</v>
+        <v>82</v>
       </c>
       <c r="I74">
-        <v>85774400</v>
+        <v>2030481726</v>
       </c>
     </row>
     <row r="75">
@@ -3115,16 +3115,16 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Chờ ký PLHĐ</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E75">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F75">
         <v>1</v>
@@ -3133,10 +3133,10 @@
         <v>1</v>
       </c>
       <c r="H75">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="I75">
-        <v>157407407</v>
+        <v>85774400</v>
       </c>
     </row>
     <row r="76">
@@ -3157,23 +3157,23 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Chờ ký PLHĐ</t>
         </is>
       </c>
       <c r="E76">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="F76">
         <v>1</v>
       </c>
       <c r="G76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H76">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I76">
-        <v>454820000</v>
+        <v>157407407</v>
       </c>
     </row>
     <row r="77">
@@ -3194,23 +3194,23 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E77">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F77">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G77">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H77">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="I77">
-        <v>746260088</v>
+        <v>454820000</v>
       </c>
     </row>
     <row r="78">
@@ -3231,23 +3231,23 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Đã hoàn thành</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E78">
-        <v>25</v>
+        <v>107</v>
       </c>
       <c r="F78">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G78">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H78">
-        <v>25</v>
+        <v>83</v>
       </c>
       <c r="I78">
-        <v>125000000</v>
+        <v>746260088</v>
       </c>
     </row>
     <row r="79">
@@ -3258,33 +3258,33 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Đã hoàn thành</t>
         </is>
       </c>
       <c r="E79">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="F79">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G79">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H79">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="I79">
-        <v>435619598</v>
+        <v>125000000</v>
       </c>
     </row>
     <row r="80">
@@ -3300,7 +3300,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3309,19 +3309,19 @@
         </is>
       </c>
       <c r="E80">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="F80">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G80">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H80">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="I80">
-        <v>283343703</v>
+        <v>435619598</v>
       </c>
     </row>
     <row r="81">
@@ -3332,21 +3332,21 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E81">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="F81">
         <v>2</v>
@@ -3355,10 +3355,10 @@
         <v>2</v>
       </c>
       <c r="H81">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="I81">
-        <v>149602776</v>
+        <v>283343703</v>
       </c>
     </row>
     <row r="82">
@@ -3379,23 +3379,23 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E82">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F82">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G82">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H82">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I82">
-        <v>120370370</v>
+        <v>149602776</v>
       </c>
     </row>
     <row r="83">
@@ -3411,16 +3411,16 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E83">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F83">
         <v>1</v>
@@ -3429,10 +3429,10 @@
         <v>1</v>
       </c>
       <c r="H83">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="I83">
-        <v>178703703</v>
+        <v>120370370</v>
       </c>
     </row>
     <row r="84">
@@ -3443,33 +3443,33 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E84">
-        <v>270</v>
+        <v>32</v>
       </c>
       <c r="F84">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G84">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H84">
-        <v>270</v>
+        <v>32</v>
       </c>
       <c r="I84">
-        <v>1441662867</v>
+        <v>178703703</v>
       </c>
     </row>
     <row r="85">
@@ -3490,23 +3490,23 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E85">
-        <v>80</v>
+        <v>270</v>
       </c>
       <c r="F85">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G85">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H85">
-        <v>18</v>
+        <v>270</v>
       </c>
       <c r="I85">
-        <v>566773049</v>
+        <v>1441662867</v>
       </c>
     </row>
     <row r="86">
@@ -3527,23 +3527,23 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E86">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="F86">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G86">
         <v>1</v>
       </c>
       <c r="H86">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="I86">
-        <v>11574074</v>
+        <v>566773049</v>
       </c>
     </row>
     <row r="87">
@@ -3559,16 +3559,16 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E87">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F87">
         <v>1</v>
@@ -3577,10 +3577,10 @@
         <v>1</v>
       </c>
       <c r="H87">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I87">
-        <v>60000000</v>
+        <v>11574074</v>
       </c>
     </row>
     <row r="88">
@@ -3591,21 +3591,21 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E88">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F88">
         <v>1</v>
@@ -3614,10 +3614,10 @@
         <v>1</v>
       </c>
       <c r="H88">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I88">
-        <v>102287036</v>
+        <v>60000000</v>
       </c>
     </row>
     <row r="89">
@@ -3638,23 +3638,23 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E89">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F89">
         <v>1</v>
       </c>
       <c r="G89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H89">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I89">
-        <v>127685185</v>
+        <v>102287036</v>
       </c>
     </row>
     <row r="90">
@@ -3675,23 +3675,23 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E90">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F90">
         <v>1</v>
       </c>
       <c r="G90">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H90">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I90">
-        <v>63435185</v>
+        <v>127685185</v>
       </c>
     </row>
     <row r="91">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3712,23 +3712,23 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E91">
-        <v>236</v>
+        <v>10</v>
       </c>
       <c r="F91">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G91">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H91">
-        <v>76</v>
+        <v>10</v>
       </c>
       <c r="I91">
-        <v>1578703703</v>
+        <v>63435185</v>
       </c>
     </row>
     <row r="92">
@@ -3744,7 +3744,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -3753,19 +3753,19 @@
         </is>
       </c>
       <c r="E92">
-        <v>5</v>
+        <v>236</v>
       </c>
       <c r="F92">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G92">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H92">
-        <v>5</v>
+        <v>76</v>
       </c>
       <c r="I92">
-        <v>10648148</v>
+        <v>1578703703</v>
       </c>
     </row>
     <row r="93">
@@ -3786,11 +3786,11 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Chờ ký PLHĐ</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E93">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="F93">
         <v>1</v>
@@ -3799,10 +3799,10 @@
         <v>1</v>
       </c>
       <c r="H93">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="I93">
-        <v>201388888</v>
+        <v>10648148</v>
       </c>
     </row>
     <row r="94">
@@ -3813,33 +3813,33 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Chờ ký PLHĐ</t>
         </is>
       </c>
       <c r="E94">
-        <v>86</v>
+        <v>28</v>
       </c>
       <c r="F94">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G94">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H94">
-        <v>86</v>
+        <v>28</v>
       </c>
       <c r="I94">
-        <v>726379627</v>
+        <v>201388888</v>
       </c>
     </row>
     <row r="95">
@@ -3860,23 +3860,23 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E95">
-        <v>14</v>
+        <v>86</v>
       </c>
       <c r="F95">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G95">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H95">
-        <v>14</v>
+        <v>86</v>
       </c>
       <c r="I95">
-        <v>110319444</v>
+        <v>726379627</v>
       </c>
     </row>
     <row r="96">
@@ -3887,7 +3887,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3897,23 +3897,23 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E96">
-        <v>222</v>
+        <v>14</v>
       </c>
       <c r="F96">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G96">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H96">
-        <v>222</v>
+        <v>14</v>
       </c>
       <c r="I96">
-        <v>1304989811</v>
+        <v>110319444</v>
       </c>
     </row>
     <row r="97">
@@ -3934,23 +3934,23 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Chờ ký PLHĐ</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E97">
-        <v>40</v>
+        <v>222</v>
       </c>
       <c r="F97">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G97">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H97">
-        <v>40</v>
+        <v>222</v>
       </c>
       <c r="I97">
-        <v>344648751</v>
+        <v>1304989811</v>
       </c>
     </row>
     <row r="98">
@@ -3971,23 +3971,23 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Chờ ký PLHĐ</t>
         </is>
       </c>
       <c r="E98">
-        <v>236</v>
+        <v>40</v>
       </c>
       <c r="F98">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G98">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H98">
-        <v>204</v>
+        <v>40</v>
       </c>
       <c r="I98">
-        <v>1371191661</v>
+        <v>344648751</v>
       </c>
     </row>
     <row r="99">
@@ -4008,23 +4008,23 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E99">
-        <v>61</v>
+        <v>236</v>
       </c>
       <c r="F99">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G99">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H99">
-        <v>61</v>
+        <v>204</v>
       </c>
       <c r="I99">
-        <v>532654574</v>
+        <v>1371191661</v>
       </c>
     </row>
     <row r="100">
@@ -4040,28 +4040,28 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E100">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="F100">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G100">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H100">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="I100">
-        <v>372057211</v>
+        <v>532654574</v>
       </c>
     </row>
     <row r="101">
@@ -4082,23 +4082,23 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E101">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F101">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G101">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H101">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="I101">
-        <v>609705554</v>
+        <v>372057211</v>
       </c>
     </row>
     <row r="102">
@@ -4109,33 +4109,33 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E102">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="F102">
         <v>3</v>
       </c>
       <c r="G102">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H102">
-        <v>28</v>
+        <v>76</v>
       </c>
       <c r="I102">
-        <v>237500000</v>
+        <v>609705554</v>
       </c>
     </row>
     <row r="103">
@@ -4156,23 +4156,23 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E103">
-        <v>68</v>
+        <v>37</v>
       </c>
       <c r="F103">
+        <v>3</v>
+      </c>
+      <c r="G103">
         <v>2</v>
       </c>
-      <c r="G103">
-        <v>1</v>
-      </c>
       <c r="H103">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="I103">
-        <v>369319030</v>
+        <v>237500000</v>
       </c>
     </row>
     <row r="104">
@@ -4193,23 +4193,23 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E104">
-        <v>12</v>
+        <v>68</v>
       </c>
       <c r="F104">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G104">
         <v>1</v>
       </c>
       <c r="H104">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I104">
-        <v>54027776</v>
+        <v>369319030</v>
       </c>
     </row>
     <row r="105">
@@ -4225,16 +4225,16 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E105">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F105">
         <v>1</v>
@@ -4243,10 +4243,10 @@
         <v>1</v>
       </c>
       <c r="H105">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I105">
-        <v>196137000</v>
+        <v>54027776</v>
       </c>
     </row>
     <row r="106">
@@ -4267,23 +4267,23 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E106">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F106">
         <v>1</v>
       </c>
       <c r="G106">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H106">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I106">
-        <v>13888888</v>
+        <v>196137000</v>
       </c>
     </row>
     <row r="107">
@@ -4294,33 +4294,33 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E107">
-        <v>249</v>
+        <v>7</v>
       </c>
       <c r="F107">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G107">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H107">
-        <v>249</v>
+        <v>0</v>
       </c>
       <c r="I107">
-        <v>1157621060</v>
+        <v>13888888</v>
       </c>
     </row>
     <row r="108">
@@ -4341,23 +4341,23 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Chờ ký PLHĐ</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E108">
-        <v>20</v>
+        <v>221</v>
       </c>
       <c r="F108">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G108">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H108">
-        <v>20</v>
+        <v>221</v>
       </c>
       <c r="I108">
-        <v>39814814</v>
+        <v>941494505</v>
       </c>
     </row>
     <row r="109">
@@ -4378,23 +4378,23 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Chờ ký PLHĐ</t>
         </is>
       </c>
       <c r="E109">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="F109">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G109">
         <v>1</v>
       </c>
       <c r="H109">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I109">
-        <v>383547036</v>
+        <v>39814814</v>
       </c>
     </row>
     <row r="110">
@@ -4405,7 +4405,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4415,23 +4415,23 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E110">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="F110">
         <v>2</v>
       </c>
       <c r="G110">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H110">
         <v>24</v>
       </c>
       <c r="I110">
-        <v>260721501</v>
+        <v>383547036</v>
       </c>
     </row>
     <row r="111">
@@ -4442,33 +4442,33 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Đã hoàn thành</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E111">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F111">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G111">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H111">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I111">
-        <v>223369390</v>
+        <v>216126555</v>
       </c>
     </row>
     <row r="112">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4493,19 +4493,19 @@
         </is>
       </c>
       <c r="E112">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="F112">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G112">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H112">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="I112">
-        <v>245787035</v>
+        <v>260721501</v>
       </c>
     </row>
     <row r="113">
@@ -4516,7 +4516,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4526,23 +4526,23 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Đã hoàn thành</t>
         </is>
       </c>
       <c r="E113">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="F113">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G113">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H113">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I113">
-        <v>86111111</v>
+        <v>223369390</v>
       </c>
     </row>
     <row r="114">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -4567,19 +4567,19 @@
         </is>
       </c>
       <c r="E114">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="F114">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G114">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H114">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="I114">
-        <v>54629629</v>
+        <v>245787035</v>
       </c>
     </row>
     <row r="115">
@@ -4590,7 +4590,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4600,23 +4600,23 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E115">
-        <v>135</v>
+        <v>13</v>
       </c>
       <c r="F115">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G115">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H115">
-        <v>129</v>
+        <v>13</v>
       </c>
       <c r="I115">
-        <v>1000769569</v>
+        <v>86111111</v>
       </c>
     </row>
     <row r="116">
@@ -4627,33 +4627,33 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E116">
-        <v>253</v>
+        <v>18</v>
       </c>
       <c r="F116">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G116">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H116">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I116">
-        <v>1151248145</v>
+        <v>54629629</v>
       </c>
     </row>
     <row r="117">
@@ -4674,23 +4674,23 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E117">
-        <v>16</v>
+        <v>111</v>
       </c>
       <c r="F117">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G117">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H117">
-        <v>16</v>
+        <v>105</v>
       </c>
       <c r="I117">
-        <v>119444444</v>
+        <v>838180551</v>
       </c>
     </row>
     <row r="118">
@@ -4706,28 +4706,28 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E118">
-        <v>113</v>
+        <v>253</v>
       </c>
       <c r="F118">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G118">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H118">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="I118">
-        <v>402701851</v>
+        <v>1151248145</v>
       </c>
     </row>
     <row r="119">
@@ -4743,7 +4743,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -4752,19 +4752,19 @@
         </is>
       </c>
       <c r="E119">
-        <v>95</v>
+        <v>16</v>
       </c>
       <c r="F119">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G119">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H119">
-        <v>95</v>
+        <v>16</v>
       </c>
       <c r="I119">
-        <v>533244443</v>
+        <v>119444444</v>
       </c>
     </row>
     <row r="120">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4785,23 +4785,23 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Đã hoàn thành</t>
         </is>
       </c>
       <c r="E120">
-        <v>30</v>
+        <v>121</v>
       </c>
       <c r="F120">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G120">
         <v>3</v>
       </c>
       <c r="H120">
-        <v>26</v>
+        <v>121</v>
       </c>
       <c r="I120">
-        <v>273939027</v>
+        <v>505181610</v>
       </c>
     </row>
     <row r="121">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -4826,19 +4826,19 @@
         </is>
       </c>
       <c r="E121">
-        <v>451</v>
+        <v>32</v>
       </c>
       <c r="F121">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="G121">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="H121">
-        <v>451</v>
+        <v>32</v>
       </c>
       <c r="I121">
-        <v>2551933598</v>
+        <v>171220370</v>
       </c>
     </row>
     <row r="122">
@@ -4849,33 +4849,33 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Chờ ký PLHĐ</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E122">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="F122">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G122">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H122">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="I122">
-        <v>180555555</v>
+        <v>422133332</v>
       </c>
     </row>
     <row r="123">
@@ -4886,7 +4886,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4896,23 +4896,23 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E123">
-        <v>103</v>
+        <v>30</v>
       </c>
       <c r="F123">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G123">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H123">
-        <v>93</v>
+        <v>26</v>
       </c>
       <c r="I123">
-        <v>705237961</v>
+        <v>273939027</v>
       </c>
     </row>
     <row r="124">
@@ -4933,23 +4933,23 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E124">
-        <v>68</v>
+        <v>451</v>
       </c>
       <c r="F124">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="G124">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="H124">
-        <v>68</v>
+        <v>451</v>
       </c>
       <c r="I124">
-        <v>397222221</v>
+        <v>2551933598</v>
       </c>
     </row>
     <row r="125">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4970,23 +4970,23 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Chờ ký PLHĐ</t>
         </is>
       </c>
       <c r="E125">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="F125">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G125">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H125">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="I125">
-        <v>106453703</v>
+        <v>180555555</v>
       </c>
     </row>
     <row r="126">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -5007,11 +5007,11 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E126">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="F126">
         <v>6</v>
@@ -5020,10 +5020,10 @@
         <v>5</v>
       </c>
       <c r="H126">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="I126">
-        <v>818903663</v>
+        <v>705237961</v>
       </c>
     </row>
     <row r="127">
@@ -5034,7 +5034,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -5044,23 +5044,23 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Chờ ký PLHĐ</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E127">
-        <v>10</v>
+        <v>68</v>
       </c>
       <c r="F127">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G127">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H127">
-        <v>10</v>
+        <v>68</v>
       </c>
       <c r="I127">
-        <v>103122222</v>
+        <v>397222221</v>
       </c>
     </row>
     <row r="128">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -5081,23 +5081,23 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E128">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="F128">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G128">
         <v>1</v>
       </c>
       <c r="H128">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I128">
-        <v>361111110</v>
+        <v>106453703</v>
       </c>
     </row>
     <row r="129">
@@ -5118,23 +5118,23 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E129">
-        <v>88</v>
+        <v>131</v>
       </c>
       <c r="F129">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G129">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H129">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="I129">
-        <v>461184182</v>
+        <v>818903663</v>
       </c>
     </row>
     <row r="130">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -5155,23 +5155,23 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Chờ ký PLHĐ</t>
         </is>
       </c>
       <c r="E130">
-        <v>118</v>
+        <v>10</v>
       </c>
       <c r="F130">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G130">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H130">
-        <v>114</v>
+        <v>10</v>
       </c>
       <c r="I130">
-        <v>485185183</v>
+        <v>103122222</v>
       </c>
     </row>
     <row r="131">
@@ -5182,7 +5182,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -5196,30 +5196,30 @@
         </is>
       </c>
       <c r="E131">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="F131">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G131">
         <v>1</v>
       </c>
       <c r="H131">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I131">
-        <v>108900925</v>
+        <v>361111110</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -5229,34 +5229,34 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E132">
-        <v>12</v>
+        <v>88</v>
       </c>
       <c r="F132">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G132">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H132">
-        <v>12</v>
+        <v>88</v>
       </c>
       <c r="I132">
-        <v>122222222</v>
+        <v>461184182</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -5270,30 +5270,30 @@
         </is>
       </c>
       <c r="E133">
-        <v>198</v>
+        <v>118</v>
       </c>
       <c r="F133">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="G133">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H133">
-        <v>182</v>
+        <v>114</v>
       </c>
       <c r="I133">
-        <v>1545608652</v>
+        <v>485185183</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -5303,23 +5303,23 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E134">
-        <v>62</v>
+        <v>12</v>
       </c>
       <c r="F134">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G134">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H134">
-        <v>62</v>
+        <v>12</v>
       </c>
       <c r="I134">
-        <v>301851851</v>
+        <v>108900925</v>
       </c>
     </row>
     <row r="135">
@@ -5330,7 +5330,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>CBG</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5344,19 +5344,19 @@
         </is>
       </c>
       <c r="E135">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="F135">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G135">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H135">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="I135">
-        <v>402314814</v>
+        <v>122222222</v>
       </c>
     </row>
     <row r="136">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5381,19 +5381,19 @@
         </is>
       </c>
       <c r="E136">
-        <v>10</v>
+        <v>198</v>
       </c>
       <c r="F136">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G136">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H136">
-        <v>10</v>
+        <v>198</v>
       </c>
       <c r="I136">
-        <v>116666666</v>
+        <v>1545608652</v>
       </c>
     </row>
     <row r="137">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5414,11 +5414,11 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Chờ hàng CNCT</t>
         </is>
       </c>
       <c r="E137">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F137">
         <v>1</v>
@@ -5427,10 +5427,10 @@
         <v>1</v>
       </c>
       <c r="H137">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I137">
-        <v>185185185</v>
+        <v>94537037</v>
       </c>
     </row>
     <row r="138">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5451,14 +5451,14 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E138">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="F138">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G138">
         <v>0</v>
@@ -5467,7 +5467,7 @@
         <v>0</v>
       </c>
       <c r="I138">
-        <v>108333333</v>
+        <v>429053702</v>
       </c>
     </row>
     <row r="139">
@@ -5478,7 +5478,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5492,7 +5492,7 @@
         </is>
       </c>
       <c r="E139">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="F139">
         <v>2</v>
@@ -5501,10 +5501,10 @@
         <v>2</v>
       </c>
       <c r="H139">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="I139">
-        <v>278333333</v>
+        <v>301851851</v>
       </c>
     </row>
     <row r="140">
@@ -5515,7 +5515,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>DBN</t>
+          <t>CBG</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5529,19 +5529,19 @@
         </is>
       </c>
       <c r="E140">
-        <v>130</v>
+        <v>46</v>
       </c>
       <c r="F140">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G140">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H140">
-        <v>130</v>
+        <v>46</v>
       </c>
       <c r="I140">
-        <v>1028518516</v>
+        <v>402314814</v>
       </c>
     </row>
     <row r="141">
@@ -5552,7 +5552,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>DBN</t>
+          <t>CBG</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Chờ ký PLHĐ</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E141">
@@ -5578,7 +5578,7 @@
         <v>18</v>
       </c>
       <c r="I141">
-        <v>145277777</v>
+        <v>148879629</v>
       </c>
     </row>
     <row r="142">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5603,19 +5603,19 @@
         </is>
       </c>
       <c r="E142">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F142">
         <v>1</v>
       </c>
       <c r="G142">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H142">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I142">
-        <v>41666666</v>
+        <v>116666666</v>
       </c>
     </row>
     <row r="143">
@@ -5626,7 +5626,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5636,23 +5636,23 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E143">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="F143">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G143">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H143">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="I143">
-        <v>459259258</v>
+        <v>185185185</v>
       </c>
     </row>
     <row r="144">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5673,11 +5673,11 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Chưa có nhân viên thực hiện</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E144">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F144">
         <v>1</v>
@@ -5689,7 +5689,7 @@
         <v>0</v>
       </c>
       <c r="I144">
-        <v>89731481</v>
+        <v>108333333</v>
       </c>
     </row>
     <row r="145">
@@ -5700,7 +5700,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5710,23 +5710,23 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E145">
-        <v>502</v>
+        <v>30</v>
       </c>
       <c r="F145">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="G145">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="H145">
-        <v>337</v>
+        <v>30</v>
       </c>
       <c r="I145">
-        <v>3920356145</v>
+        <v>278333333</v>
       </c>
     </row>
     <row r="146">
@@ -5737,7 +5737,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>DBN</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5747,23 +5747,23 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E146">
-        <v>190</v>
+        <v>130</v>
       </c>
       <c r="F146">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G146">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H146">
-        <v>190</v>
+        <v>130</v>
       </c>
       <c r="I146">
-        <v>806674721</v>
+        <v>1028518516</v>
       </c>
     </row>
     <row r="147">
@@ -5774,33 +5774,33 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>DBN</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Chờ ký PLHĐ</t>
         </is>
       </c>
       <c r="E147">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F147">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G147">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H147">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I147">
-        <v>179694444</v>
+        <v>145277777</v>
       </c>
     </row>
     <row r="148">
@@ -5811,33 +5811,33 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E148">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="F148">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G148">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H148">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I148">
-        <v>186868952</v>
+        <v>41666666</v>
       </c>
     </row>
     <row r="149">
@@ -5848,7 +5848,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5862,19 +5862,19 @@
         </is>
       </c>
       <c r="E149">
-        <v>157</v>
+        <v>64</v>
       </c>
       <c r="F149">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G149">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="H149">
-        <v>157</v>
+        <v>44</v>
       </c>
       <c r="I149">
-        <v>1420701846</v>
+        <v>459259258</v>
       </c>
     </row>
     <row r="150">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5895,11 +5895,11 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Chưa có nhân viên thực hiện</t>
         </is>
       </c>
       <c r="E150">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F150">
         <v>1</v>
@@ -5911,7 +5911,7 @@
         <v>0</v>
       </c>
       <c r="I150">
-        <v>240740740</v>
+        <v>89731481</v>
       </c>
     </row>
     <row r="151">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5932,23 +5932,23 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E151">
-        <v>120</v>
+        <v>502</v>
       </c>
       <c r="F151">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="G151">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H151">
-        <v>120</v>
+        <v>402</v>
       </c>
       <c r="I151">
-        <v>941087651</v>
+        <v>3920356145</v>
       </c>
     </row>
     <row r="152">
@@ -5959,7 +5959,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5969,23 +5969,23 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Đã hoàn thành</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E152">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="F152">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G152">
         <v>1</v>
       </c>
       <c r="H152">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I152">
-        <v>146296296</v>
+        <v>579166663</v>
       </c>
     </row>
     <row r="153">
@@ -5996,12 +5996,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -6010,19 +6010,19 @@
         </is>
       </c>
       <c r="E153">
-        <v>6</v>
+        <v>178</v>
       </c>
       <c r="F153">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G153">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H153">
-        <v>6</v>
+        <v>178</v>
       </c>
       <c r="I153">
-        <v>15740740</v>
+        <v>700193240</v>
       </c>
     </row>
     <row r="154">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -6047,19 +6047,19 @@
         </is>
       </c>
       <c r="E154">
-        <v>192</v>
+        <v>25</v>
       </c>
       <c r="F154">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G154">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H154">
-        <v>192</v>
+        <v>25</v>
       </c>
       <c r="I154">
-        <v>728703702</v>
+        <v>179694444</v>
       </c>
     </row>
     <row r="155">
@@ -6070,33 +6070,33 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Chờ ký PLHĐ</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E155">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="F155">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G155">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H155">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="I155">
-        <v>105555555</v>
+        <v>186868952</v>
       </c>
     </row>
     <row r="156">
@@ -6107,7 +6107,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -6121,19 +6121,19 @@
         </is>
       </c>
       <c r="E156">
-        <v>395</v>
+        <v>121</v>
       </c>
       <c r="F156">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="G156">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="H156">
-        <v>328</v>
+        <v>121</v>
       </c>
       <c r="I156">
-        <v>3718551107</v>
+        <v>1139220366</v>
       </c>
     </row>
     <row r="157">
@@ -6144,7 +6144,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -6154,23 +6154,23 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E157">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F157">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G157">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H157">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I157">
-        <v>283796296</v>
+        <v>240740740</v>
       </c>
     </row>
     <row r="158">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -6195,19 +6195,19 @@
         </is>
       </c>
       <c r="E158">
-        <v>8</v>
+        <v>156</v>
       </c>
       <c r="F158">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G158">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H158">
-        <v>8</v>
+        <v>156</v>
       </c>
       <c r="I158">
-        <v>28703703</v>
+        <v>1222569131</v>
       </c>
     </row>
     <row r="159">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -6228,23 +6228,23 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Đã hoàn thành</t>
         </is>
       </c>
       <c r="E159">
-        <v>362</v>
+        <v>20</v>
       </c>
       <c r="F159">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="G159">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="H159">
-        <v>256</v>
+        <v>20</v>
       </c>
       <c r="I159">
-        <v>3355957586</v>
+        <v>146296296</v>
       </c>
     </row>
     <row r="160">
@@ -6255,12 +6255,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -6269,19 +6269,19 @@
         </is>
       </c>
       <c r="E160">
-        <v>62</v>
+        <v>6</v>
       </c>
       <c r="F160">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G160">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H160">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="I160">
-        <v>347456218</v>
+        <v>15740740</v>
       </c>
     </row>
     <row r="161">
@@ -6292,21 +6292,21 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Chờ ký PLHĐ</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E161">
-        <v>103</v>
+        <v>192</v>
       </c>
       <c r="F161">
         <v>4</v>
@@ -6315,10 +6315,10 @@
         <v>4</v>
       </c>
       <c r="H161">
-        <v>103</v>
+        <v>192</v>
       </c>
       <c r="I161">
-        <v>747324666</v>
+        <v>728703702</v>
       </c>
     </row>
     <row r="162">
@@ -6329,21 +6329,21 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Chờ ký PLHĐ</t>
         </is>
       </c>
       <c r="E162">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="F162">
         <v>1</v>
@@ -6352,10 +6352,10 @@
         <v>1</v>
       </c>
       <c r="H162">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="I162">
-        <v>163273500</v>
+        <v>105555555</v>
       </c>
     </row>
     <row r="163">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -6380,19 +6380,19 @@
         </is>
       </c>
       <c r="E163">
-        <v>295</v>
+        <v>379</v>
       </c>
       <c r="F163">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="G163">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="H163">
-        <v>268</v>
+        <v>341</v>
       </c>
       <c r="I163">
-        <v>2247145244</v>
+        <v>3577557107</v>
       </c>
     </row>
     <row r="164">
@@ -6403,7 +6403,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -6417,10 +6417,10 @@
         </is>
       </c>
       <c r="E164">
-        <v>16</v>
+        <v>97</v>
       </c>
       <c r="F164">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G164">
         <v>0</v>
@@ -6429,7 +6429,7 @@
         <v>0</v>
       </c>
       <c r="I164">
-        <v>129788868</v>
+        <v>846995818</v>
       </c>
     </row>
     <row r="165">
@@ -6440,7 +6440,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -6454,19 +6454,19 @@
         </is>
       </c>
       <c r="E165">
-        <v>98</v>
+        <v>46</v>
       </c>
       <c r="F165">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G165">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H165">
-        <v>98</v>
+        <v>46</v>
       </c>
       <c r="I165">
-        <v>697187890</v>
+        <v>424790296</v>
       </c>
     </row>
     <row r="166">
@@ -6477,33 +6477,33 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E166">
-        <v>304</v>
+        <v>8</v>
       </c>
       <c r="F166">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="G166">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="H166">
-        <v>290</v>
+        <v>8</v>
       </c>
       <c r="I166">
-        <v>2724380081</v>
+        <v>28703703</v>
       </c>
     </row>
     <row r="167">
@@ -6514,7 +6514,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -6528,19 +6528,19 @@
         </is>
       </c>
       <c r="E167">
-        <v>254</v>
+        <v>350</v>
       </c>
       <c r="F167">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G167">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H167">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="I167">
-        <v>1971925128</v>
+        <v>3254138336</v>
       </c>
     </row>
     <row r="168">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -6561,23 +6561,23 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Chờ hàng TTQH</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E168">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="F168">
         <v>1</v>
       </c>
       <c r="G168">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H168">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I168">
-        <v>44907407</v>
+        <v>178560600</v>
       </c>
     </row>
     <row r="169">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -6598,23 +6598,23 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Chờ ký PLHĐ</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E169">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="F169">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G169">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H169">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="I169">
-        <v>107751275</v>
+        <v>449275468</v>
       </c>
     </row>
     <row r="170">
@@ -6625,33 +6625,33 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Chờ ký PLHĐ</t>
         </is>
       </c>
       <c r="E170">
-        <v>12</v>
+        <v>103</v>
       </c>
       <c r="F170">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G170">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H170">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="I170">
-        <v>106092592</v>
+        <v>747324666</v>
       </c>
     </row>
     <row r="171">
@@ -6662,33 +6662,33 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E171">
-        <v>110</v>
+        <v>32</v>
       </c>
       <c r="F171">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G171">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H171">
-        <v>96</v>
+        <v>32</v>
       </c>
       <c r="I171">
-        <v>926398145</v>
+        <v>163273500</v>
       </c>
     </row>
     <row r="172">
@@ -6699,7 +6699,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -6709,23 +6709,23 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Chờ ký PLHĐ</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E172">
-        <v>14</v>
+        <v>295</v>
       </c>
       <c r="F172">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="G172">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="H172">
-        <v>14</v>
+        <v>295</v>
       </c>
       <c r="I172">
-        <v>125416666</v>
+        <v>2247145244</v>
       </c>
     </row>
     <row r="173">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -6746,23 +6746,23 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E173">
-        <v>96</v>
+        <v>16</v>
       </c>
       <c r="F173">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G173">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H173">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="I173">
-        <v>436111110</v>
+        <v>129788868</v>
       </c>
     </row>
     <row r="174">
@@ -6773,7 +6773,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -6783,23 +6783,23 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E174">
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="F174">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G174">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H174">
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="I174">
-        <v>597786109</v>
+        <v>697187890</v>
       </c>
     </row>
     <row r="175">
@@ -6810,33 +6810,33 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>LCU</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E175">
-        <v>36</v>
+        <v>276</v>
       </c>
       <c r="F175">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="G175">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="H175">
-        <v>36</v>
+        <v>276</v>
       </c>
       <c r="I175">
-        <v>260451851</v>
+        <v>2480786100</v>
       </c>
     </row>
     <row r="176">
@@ -6847,7 +6847,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -6857,23 +6857,23 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Chờ ký PLHĐ</t>
         </is>
       </c>
       <c r="E176">
-        <v>141</v>
+        <v>14</v>
       </c>
       <c r="F176">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G176">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H176">
-        <v>100</v>
+        <v>14</v>
       </c>
       <c r="I176">
-        <v>979676848</v>
+        <v>118593981</v>
       </c>
     </row>
     <row r="177">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -6894,23 +6894,23 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E177">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F177">
         <v>1</v>
       </c>
       <c r="G177">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H177">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I177">
-        <v>104629629</v>
+        <v>125000000</v>
       </c>
     </row>
     <row r="178">
@@ -6921,7 +6921,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -6935,19 +6935,19 @@
         </is>
       </c>
       <c r="E178">
-        <v>164</v>
+        <v>254</v>
       </c>
       <c r="F178">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="G178">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="H178">
-        <v>164</v>
+        <v>254</v>
       </c>
       <c r="I178">
-        <v>1222473144</v>
+        <v>1971925128</v>
       </c>
     </row>
     <row r="179">
@@ -6958,7 +6958,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -6968,23 +6968,23 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Chờ hàng TTQH</t>
         </is>
       </c>
       <c r="E179">
-        <v>748</v>
+        <v>2</v>
       </c>
       <c r="F179">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="G179">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="H179">
-        <v>564</v>
+        <v>2</v>
       </c>
       <c r="I179">
-        <v>6702367383</v>
+        <v>44907407</v>
       </c>
     </row>
     <row r="180">
@@ -6995,7 +6995,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -7005,23 +7005,23 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Chờ ký PLHĐ</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E180">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="F180">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G180">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H180">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="I180">
-        <v>475708332</v>
+        <v>674522718</v>
       </c>
     </row>
     <row r="181">
@@ -7032,12 +7032,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -7046,19 +7046,19 @@
         </is>
       </c>
       <c r="E181">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="F181">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G181">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H181">
-        <v>50</v>
+        <v>96</v>
       </c>
       <c r="I181">
-        <v>427962962</v>
+        <v>926398145</v>
       </c>
     </row>
     <row r="182">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -7083,7 +7083,7 @@
         </is>
       </c>
       <c r="E182">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F182">
         <v>1</v>
@@ -7092,10 +7092,10 @@
         <v>1</v>
       </c>
       <c r="H182">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I182">
-        <v>123733333</v>
+        <v>125416666</v>
       </c>
     </row>
     <row r="183">
@@ -7106,33 +7106,33 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E183">
-        <v>307</v>
+        <v>32</v>
       </c>
       <c r="F183">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="G183">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H183">
-        <v>307</v>
+        <v>0</v>
       </c>
       <c r="I183">
-        <v>2706348784</v>
+        <v>263647117</v>
       </c>
     </row>
     <row r="184">
@@ -7143,7 +7143,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -7153,23 +7153,23 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E184">
-        <v>126</v>
+        <v>96</v>
       </c>
       <c r="F184">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G184">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H184">
-        <v>126</v>
+        <v>96</v>
       </c>
       <c r="I184">
-        <v>1049882081</v>
+        <v>436111110</v>
       </c>
     </row>
     <row r="185">
@@ -7180,7 +7180,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -7190,23 +7190,23 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E185">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="F185">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G185">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H185">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="I185">
-        <v>149606000</v>
+        <v>597786109</v>
       </c>
     </row>
     <row r="186">
@@ -7217,7 +7217,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>LCU</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -7231,7 +7231,7 @@
         </is>
       </c>
       <c r="E186">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="F186">
         <v>1</v>
@@ -7240,10 +7240,10 @@
         <v>1</v>
       </c>
       <c r="H186">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="I186">
-        <v>190043150</v>
+        <v>260451851</v>
       </c>
     </row>
     <row r="187">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -7268,19 +7268,19 @@
         </is>
       </c>
       <c r="E187">
-        <v>455</v>
+        <v>141</v>
       </c>
       <c r="F187">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="G187">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="H187">
-        <v>357</v>
+        <v>136</v>
       </c>
       <c r="I187">
-        <v>3396298983</v>
+        <v>979676848</v>
       </c>
     </row>
     <row r="188">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -7305,10 +7305,10 @@
         </is>
       </c>
       <c r="E188">
-        <v>56</v>
+        <v>100</v>
       </c>
       <c r="F188">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G188">
         <v>0</v>
@@ -7317,7 +7317,7 @@
         <v>0</v>
       </c>
       <c r="I188">
-        <v>361111111</v>
+        <v>495361108</v>
       </c>
     </row>
     <row r="189">
@@ -7328,7 +7328,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -7342,19 +7342,19 @@
         </is>
       </c>
       <c r="E189">
-        <v>95</v>
+        <v>10</v>
       </c>
       <c r="F189">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G189">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H189">
-        <v>95</v>
+        <v>10</v>
       </c>
       <c r="I189">
-        <v>969444443</v>
+        <v>104629629</v>
       </c>
     </row>
     <row r="190">
@@ -7365,33 +7365,33 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E190">
-        <v>50</v>
+        <v>164</v>
       </c>
       <c r="F190">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G190">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H190">
-        <v>50</v>
+        <v>164</v>
       </c>
       <c r="I190">
-        <v>446499073</v>
+        <v>1222473144</v>
       </c>
     </row>
     <row r="191">
@@ -7402,7 +7402,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -7412,23 +7412,23 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E191">
-        <v>511</v>
+        <v>38</v>
       </c>
       <c r="F191">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="G191">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="H191">
-        <v>324</v>
+        <v>0</v>
       </c>
       <c r="I191">
-        <v>3538170871</v>
+        <v>286325925</v>
       </c>
     </row>
     <row r="192">
@@ -7439,7 +7439,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -7449,23 +7449,23 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Chờ ký PLHĐ</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E192">
-        <v>39</v>
+        <v>664</v>
       </c>
       <c r="F192">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="G192">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="H192">
-        <v>39</v>
+        <v>604</v>
       </c>
       <c r="I192">
-        <v>301076660</v>
+        <v>5875980349</v>
       </c>
     </row>
     <row r="193">
@@ -7476,7 +7476,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -7486,23 +7486,23 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Chờ ký PLHĐ</t>
         </is>
       </c>
       <c r="E193">
-        <v>42</v>
+        <v>84</v>
       </c>
       <c r="F193">
         <v>4</v>
       </c>
       <c r="G193">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H193">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="I193">
-        <v>319486468</v>
+        <v>743580553</v>
       </c>
     </row>
     <row r="194">
@@ -7513,7 +7513,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -7523,23 +7523,23 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E194">
-        <v>16</v>
+        <v>116</v>
       </c>
       <c r="F194">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G194">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H194">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="I194">
-        <v>131277777</v>
+        <v>998410937</v>
       </c>
     </row>
     <row r="195">
@@ -7550,7 +7550,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -7560,11 +7560,11 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Chờ ký PLHĐ</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E195">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F195">
         <v>1</v>
@@ -7573,10 +7573,10 @@
         <v>1</v>
       </c>
       <c r="H195">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="I195">
-        <v>166296296</v>
+        <v>113155555</v>
       </c>
     </row>
     <row r="196">
@@ -7587,33 +7587,33 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E196">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="F196">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G196">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H196">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="I196">
-        <v>208333333</v>
+        <v>551696295</v>
       </c>
     </row>
     <row r="197">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -7638,19 +7638,19 @@
         </is>
       </c>
       <c r="E197">
-        <v>10</v>
+        <v>349</v>
       </c>
       <c r="F197">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="G197">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="H197">
-        <v>10</v>
+        <v>349</v>
       </c>
       <c r="I197">
-        <v>96357716</v>
+        <v>3151708042</v>
       </c>
     </row>
     <row r="198">
@@ -7661,7 +7661,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>SLA</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -7675,19 +7675,19 @@
         </is>
       </c>
       <c r="E198">
-        <v>46</v>
+        <v>110</v>
       </c>
       <c r="F198">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G198">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H198">
-        <v>46</v>
+        <v>110</v>
       </c>
       <c r="I198">
-        <v>309527777</v>
+        <v>911096711</v>
       </c>
     </row>
     <row r="199">
@@ -7698,7 +7698,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -7708,23 +7708,23 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E199">
-        <v>824</v>
+        <v>24</v>
       </c>
       <c r="F199">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="G199">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="H199">
-        <v>718</v>
+        <v>0</v>
       </c>
       <c r="I199">
-        <v>5854656845</v>
+        <v>163494888</v>
       </c>
     </row>
     <row r="200">
@@ -7735,7 +7735,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -7745,11 +7745,11 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Chờ ký PLHĐ</t>
+          <t>Đã hoàn thành</t>
         </is>
       </c>
       <c r="E200">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F200">
         <v>1</v>
@@ -7758,10 +7758,10 @@
         <v>1</v>
       </c>
       <c r="H200">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I200">
-        <v>133055555</v>
+        <v>138785370</v>
       </c>
     </row>
     <row r="201">
@@ -7772,21 +7772,21 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E201">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="F201">
         <v>1</v>
@@ -7795,10 +7795,10 @@
         <v>1</v>
       </c>
       <c r="H201">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="I201">
-        <v>111111111</v>
+        <v>190043150</v>
       </c>
     </row>
     <row r="202">
@@ -7809,7 +7809,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -7819,23 +7819,23 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E202">
-        <v>70</v>
+        <v>429</v>
       </c>
       <c r="F202">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="G202">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="H202">
-        <v>70</v>
+        <v>379</v>
       </c>
       <c r="I202">
-        <v>557777776</v>
+        <v>3145025604</v>
       </c>
     </row>
     <row r="203">
@@ -7846,33 +7846,33 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E203">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F203">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G203">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H203">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I203">
-        <v>444753085</v>
+        <v>361111111</v>
       </c>
     </row>
     <row r="204">
@@ -7883,21 +7883,21 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Chờ ký PLHĐ</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E204">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="F204">
         <v>1</v>
@@ -7906,10 +7906,10 @@
         <v>1</v>
       </c>
       <c r="H204">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="I204">
-        <v>89814814</v>
+        <v>578703703</v>
       </c>
     </row>
     <row r="205">
@@ -7920,7 +7920,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -7934,19 +7934,19 @@
         </is>
       </c>
       <c r="E205">
-        <v>354</v>
+        <v>123</v>
       </c>
       <c r="F205">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G205">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H205">
-        <v>354</v>
+        <v>123</v>
       </c>
       <c r="I205">
-        <v>2232390710</v>
+        <v>1088513192</v>
       </c>
     </row>
     <row r="206">
@@ -7957,7 +7957,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -7971,19 +7971,19 @@
         </is>
       </c>
       <c r="E206">
-        <v>127</v>
+        <v>499</v>
       </c>
       <c r="F206">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="G206">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="H206">
-        <v>65</v>
+        <v>326</v>
       </c>
       <c r="I206">
-        <v>765306014</v>
+        <v>3435380192</v>
       </c>
     </row>
     <row r="207">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -8004,23 +8004,23 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Chờ ký PLHĐ</t>
         </is>
       </c>
       <c r="E207">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="F207">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G207">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H207">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="I207">
-        <v>102129629</v>
+        <v>301076660</v>
       </c>
     </row>
     <row r="208">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -8041,23 +8041,23 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E208">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="F208">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G208">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H208">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="I208">
-        <v>270579836</v>
+        <v>112768518</v>
       </c>
     </row>
     <row r="209">
@@ -8068,7 +8068,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -8078,23 +8078,23 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Chờ ký PLHĐ</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E209">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F209">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G209">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H209">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="I209">
-        <v>571568517</v>
+        <v>422277147</v>
       </c>
     </row>
     <row r="210">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -8119,30 +8119,30 @@
         </is>
       </c>
       <c r="E210">
-        <v>107</v>
+        <v>2</v>
       </c>
       <c r="F210">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G210">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H210">
-        <v>97</v>
+        <v>2</v>
       </c>
       <c r="I210">
-        <v>667325924</v>
+        <v>11833333</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -8152,34 +8152,34 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Chờ hàng TTQH</t>
+          <t>Chờ ký PLHĐ</t>
         </is>
       </c>
       <c r="E211">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="F211">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G211">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H211">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="I211">
-        <v>1818181</v>
+        <v>285740740</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -8189,34 +8189,34 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E212">
-        <v>7</v>
+        <v>46</v>
       </c>
       <c r="F212">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G212">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H212">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I212">
-        <v>12798526</v>
+        <v>208333333</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -8226,71 +8226,71 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E213">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F213">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G213">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H213">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I213">
-        <v>3703702</v>
+        <v>96357716</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>SLA</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E214">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="F214">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G214">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H214">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="I214">
-        <v>154638888</v>
+        <v>309527777</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -8304,30 +8304,30 @@
         </is>
       </c>
       <c r="E215">
-        <v>15</v>
+        <v>812</v>
       </c>
       <c r="F215">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="G215">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="H215">
-        <v>15</v>
+        <v>720</v>
       </c>
       <c r="I215">
-        <v>72296140</v>
+        <v>5739286474</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -8337,108 +8337,108 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Chờ ký PLHĐ</t>
         </is>
       </c>
       <c r="E216">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="F216">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G216">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H216">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="I216">
-        <v>116012600</v>
+        <v>258055555</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E217">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="F217">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G217">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H217">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I217">
-        <v>27777777</v>
+        <v>351057407</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Chờ ký PLHĐ</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E218">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="F218">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G218">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H218">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="I218">
-        <v>150959643</v>
+        <v>557777776</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -8448,39 +8448,39 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Đã hoàn thành</t>
         </is>
       </c>
       <c r="E219">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="F219">
         <v>1</v>
       </c>
       <c r="G219">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H219">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I219">
-        <v>3542600</v>
+        <v>125000000</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -8489,72 +8489,72 @@
         </is>
       </c>
       <c r="E220">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="F220">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G220">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H220">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="I220">
-        <v>129629629</v>
+        <v>444753085</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Chờ ký PLHĐ</t>
         </is>
       </c>
       <c r="E221">
-        <v>153</v>
+        <v>18</v>
       </c>
       <c r="F221">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G221">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H221">
-        <v>153</v>
+        <v>18</v>
       </c>
       <c r="I221">
-        <v>1313925785</v>
+        <v>89814814</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -8563,30 +8563,30 @@
         </is>
       </c>
       <c r="E222">
-        <v>24</v>
+        <v>340</v>
       </c>
       <c r="F222">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="G222">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="H222">
-        <v>24</v>
+        <v>340</v>
       </c>
       <c r="I222">
-        <v>186500000</v>
+        <v>2107390710</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -8600,30 +8600,30 @@
         </is>
       </c>
       <c r="E223">
-        <v>31</v>
+        <v>127</v>
       </c>
       <c r="F223">
+        <v>7</v>
+      </c>
+      <c r="G223">
         <v>4</v>
       </c>
-      <c r="G223">
-        <v>3</v>
-      </c>
       <c r="H223">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="I223">
-        <v>245645065</v>
+        <v>765306014</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -8633,34 +8633,34 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E224">
-        <v>6</v>
+        <v>130</v>
       </c>
       <c r="F224">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G224">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H224">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I224">
-        <v>57407407</v>
+        <v>916976848</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -8674,30 +8674,30 @@
         </is>
       </c>
       <c r="E225">
-        <v>310</v>
+        <v>44</v>
       </c>
       <c r="F225">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="G225">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="H225">
-        <v>243</v>
+        <v>44</v>
       </c>
       <c r="I225">
-        <v>2651792353</v>
+        <v>270579836</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -8707,71 +8707,71 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Đã hoàn thành</t>
+          <t>Chờ ký PLHĐ</t>
         </is>
       </c>
       <c r="E226">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="F226">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G226">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H226">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="I226">
-        <v>114602777</v>
+        <v>571568517</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E227">
-        <v>8</v>
+        <v>107</v>
       </c>
       <c r="F227">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G227">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H227">
-        <v>8</v>
+        <v>97</v>
       </c>
       <c r="I227">
-        <v>92592592</v>
+        <v>667325924</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -8781,34 +8781,34 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E228">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="F228">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G228">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H228">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="I228">
-        <v>410623414</v>
+        <v>109074074</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -8818,11 +8818,11 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Chờ ký PLHĐ</t>
+          <t>Chờ hàng TTQH</t>
         </is>
       </c>
       <c r="E229">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="F229">
         <v>1</v>
@@ -8834,18 +8834,18 @@
         <v>0</v>
       </c>
       <c r="I229">
-        <v>169874623</v>
+        <v>1818181</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -8855,34 +8855,34 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Chờ ký PLHĐ</t>
         </is>
       </c>
       <c r="E230">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="F230">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G230">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H230">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="I230">
-        <v>241810184</v>
+        <v>12798526</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -8896,67 +8896,67 @@
         </is>
       </c>
       <c r="E231">
-        <v>106</v>
+        <v>2</v>
       </c>
       <c r="F231">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G231">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H231">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="I231">
-        <v>779297220</v>
+        <v>3703702</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E232">
         <v>16</v>
       </c>
       <c r="F232">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G232">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H232">
         <v>16</v>
       </c>
       <c r="I232">
-        <v>185648147</v>
+        <v>154638888</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -8970,30 +8970,30 @@
         </is>
       </c>
       <c r="E233">
-        <v>156</v>
+        <v>15</v>
       </c>
       <c r="F233">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G233">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="H233">
-        <v>156</v>
+        <v>15</v>
       </c>
       <c r="I233">
-        <v>1318613884</v>
+        <v>72296140</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -9007,7 +9007,7 @@
         </is>
       </c>
       <c r="E234">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F234">
         <v>1</v>
@@ -9016,95 +9016,95 @@
         <v>1</v>
       </c>
       <c r="H234">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I234">
-        <v>152777777</v>
+        <v>116012600</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Đã hoàn thành</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E235">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="F235">
         <v>1</v>
       </c>
       <c r="G235">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H235">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="I235">
-        <v>287037037</v>
+        <v>27777777</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Chờ ký PLHĐ</t>
         </is>
       </c>
       <c r="E236">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="F236">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G236">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H236">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="I236">
-        <v>206098629</v>
+        <v>150959643</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -9114,34 +9114,34 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E237">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="F237">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G237">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H237">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="I237">
-        <v>681399851</v>
+        <v>3542600</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -9155,19 +9155,19 @@
         </is>
       </c>
       <c r="E238">
-        <v>223</v>
+        <v>24</v>
       </c>
       <c r="F238">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G238">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H238">
-        <v>157</v>
+        <v>24</v>
       </c>
       <c r="I238">
-        <v>1821733806</v>
+        <v>129629629</v>
       </c>
     </row>
     <row r="239">
@@ -9178,7 +9178,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -9188,23 +9188,23 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Chờ ký PLHĐ</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E239">
-        <v>44</v>
+        <v>139</v>
       </c>
       <c r="F239">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G239">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H239">
-        <v>44</v>
+        <v>139</v>
       </c>
       <c r="I239">
-        <v>354286800</v>
+        <v>1230592452</v>
       </c>
     </row>
     <row r="240">
@@ -9215,7 +9215,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -9225,23 +9225,23 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E240">
-        <v>115</v>
+        <v>60</v>
       </c>
       <c r="F240">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G240">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H240">
-        <v>115</v>
+        <v>16</v>
       </c>
       <c r="I240">
-        <v>828752973</v>
+        <v>493992592</v>
       </c>
     </row>
     <row r="241">
@@ -9252,12 +9252,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -9266,7 +9266,7 @@
         </is>
       </c>
       <c r="E241">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F241">
         <v>2</v>
@@ -9275,10 +9275,10 @@
         <v>2</v>
       </c>
       <c r="H241">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="I241">
-        <v>372325888</v>
+        <v>269833333</v>
       </c>
     </row>
     <row r="242">
@@ -9289,7 +9289,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -9303,19 +9303,19 @@
         </is>
       </c>
       <c r="E242">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F242">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G242">
         <v>2</v>
       </c>
       <c r="H242">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="I242">
-        <v>300949073</v>
+        <v>214058954</v>
       </c>
     </row>
     <row r="243">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -9336,23 +9336,23 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E243">
-        <v>235</v>
+        <v>29</v>
       </c>
       <c r="F243">
+        <v>3</v>
+      </c>
+      <c r="G243">
+        <v>1</v>
+      </c>
+      <c r="H243">
         <v>7</v>
       </c>
-      <c r="G243">
-        <v>7</v>
-      </c>
-      <c r="H243">
-        <v>235</v>
-      </c>
       <c r="I243">
-        <v>1293811423</v>
+        <v>234703703</v>
       </c>
     </row>
     <row r="244">
@@ -9363,7 +9363,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -9373,11 +9373,11 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E244">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F244">
         <v>2</v>
@@ -9386,10 +9386,10 @@
         <v>2</v>
       </c>
       <c r="H244">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="I244">
-        <v>296596296</v>
+        <v>88993518</v>
       </c>
     </row>
     <row r="245">
@@ -9400,7 +9400,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -9414,19 +9414,19 @@
         </is>
       </c>
       <c r="E245">
-        <v>74</v>
+        <v>310</v>
       </c>
       <c r="F245">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="G245">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="H245">
-        <v>74</v>
+        <v>292</v>
       </c>
       <c r="I245">
-        <v>588722955</v>
+        <v>2651792353</v>
       </c>
     </row>
     <row r="246">
@@ -9437,7 +9437,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -9447,23 +9447,23 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Đã hoàn thành</t>
         </is>
       </c>
       <c r="E246">
-        <v>279</v>
+        <v>12</v>
       </c>
       <c r="F246">
+        <v>1</v>
+      </c>
+      <c r="G246">
+        <v>1</v>
+      </c>
+      <c r="H246">
         <v>12</v>
       </c>
-      <c r="G246">
-        <v>11</v>
-      </c>
-      <c r="H246">
-        <v>245</v>
-      </c>
       <c r="I246">
-        <v>2268636397</v>
+        <v>114602777</v>
       </c>
     </row>
     <row r="247">
@@ -9474,21 +9474,21 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Chờ hàng CNCT</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E247">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F247">
         <v>1</v>
@@ -9497,10 +9497,10 @@
         <v>1</v>
       </c>
       <c r="H247">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="I247">
-        <v>81888888</v>
+        <v>92592592</v>
       </c>
     </row>
     <row r="248">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -9525,19 +9525,19 @@
         </is>
       </c>
       <c r="E248">
-        <v>152</v>
+        <v>44</v>
       </c>
       <c r="F248">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G248">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H248">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="I248">
-        <v>1055740737</v>
+        <v>410623414</v>
       </c>
     </row>
     <row r="249">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -9558,23 +9558,23 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Chờ ký PLHĐ</t>
         </is>
       </c>
       <c r="E249">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="F249">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G249">
         <v>1</v>
       </c>
       <c r="H249">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="I249">
-        <v>139768518</v>
+        <v>209689437</v>
       </c>
     </row>
     <row r="250">
@@ -9585,7 +9585,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -9595,23 +9595,23 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E250">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F250">
         <v>2</v>
       </c>
       <c r="G250">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H250">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I250">
-        <v>254242086</v>
+        <v>209785059</v>
       </c>
     </row>
     <row r="251">
@@ -9622,7 +9622,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -9632,23 +9632,23 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E251">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F251">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G251">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H251">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I251">
-        <v>284999999</v>
+        <v>241810184</v>
       </c>
     </row>
     <row r="252">
@@ -9659,7 +9659,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -9669,23 +9669,23 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E252">
-        <v>20</v>
+        <v>106</v>
       </c>
       <c r="F252">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G252">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H252">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="I252">
-        <v>146887037</v>
+        <v>779297220</v>
       </c>
     </row>
     <row r="253">
@@ -9696,7 +9696,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -9710,19 +9710,19 @@
         </is>
       </c>
       <c r="E253">
-        <v>140</v>
+        <v>16</v>
       </c>
       <c r="F253">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G253">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H253">
-        <v>105</v>
+        <v>16</v>
       </c>
       <c r="I253">
-        <v>1380296950</v>
+        <v>185648147</v>
       </c>
     </row>
     <row r="254">
@@ -9733,7 +9733,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -9743,23 +9743,23 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E254">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F254">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G254">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H254">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I254">
-        <v>107407407</v>
+        <v>106481480</v>
       </c>
     </row>
     <row r="255">
@@ -9770,7 +9770,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -9784,19 +9784,19 @@
         </is>
       </c>
       <c r="E255">
-        <v>110</v>
+        <v>146</v>
       </c>
       <c r="F255">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G255">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H255">
-        <v>98</v>
+        <v>146</v>
       </c>
       <c r="I255">
-        <v>929231107</v>
+        <v>1221391662</v>
       </c>
     </row>
     <row r="256">
@@ -9807,7 +9807,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -9817,23 +9817,23 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E256">
-        <v>144</v>
+        <v>20</v>
       </c>
       <c r="F256">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G256">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="H256">
-        <v>144</v>
+        <v>20</v>
       </c>
       <c r="I256">
-        <v>1499900786</v>
+        <v>152777777</v>
       </c>
     </row>
     <row r="257">
@@ -9844,7 +9844,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -9854,23 +9854,23 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Đã hoàn thành</t>
         </is>
       </c>
       <c r="E257">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="F257">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G257">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H257">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="I257">
-        <v>127777777</v>
+        <v>384259259</v>
       </c>
     </row>
     <row r="258">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -9895,19 +9895,19 @@
         </is>
       </c>
       <c r="E258">
-        <v>248</v>
+        <v>50</v>
       </c>
       <c r="F258">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="G258">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="H258">
-        <v>240</v>
+        <v>50</v>
       </c>
       <c r="I258">
-        <v>2198066137</v>
+        <v>206098629</v>
       </c>
     </row>
     <row r="259">
@@ -9918,7 +9918,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -9928,23 +9928,23 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Chờ ký PLHĐ</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E259">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="F259">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G259">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H259">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="I259">
-        <v>113333333</v>
+        <v>681399851</v>
       </c>
     </row>
     <row r="260">
@@ -9955,7 +9955,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -9965,34 +9965,34 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E260">
-        <v>56</v>
+        <v>223</v>
       </c>
       <c r="F260">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G260">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="H260">
-        <v>24</v>
+        <v>179</v>
       </c>
       <c r="I260">
-        <v>330625046</v>
+        <v>1821733806</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -10002,7 +10002,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Chờ ký PLHĐ</t>
         </is>
       </c>
       <c r="E261">
@@ -10012,24 +10012,24 @@
         <v>2</v>
       </c>
       <c r="G261">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H261">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="I261">
-        <v>342663644</v>
+        <v>354286800</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -10039,34 +10039,34 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E262">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="F262">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G262">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H262">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I262">
-        <v>85400000</v>
+        <v>469425782</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -10076,66 +10076,66 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Chờ ký PLHĐ</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E263">
-        <v>5</v>
+        <v>115</v>
       </c>
       <c r="F263">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G263">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H263">
-        <v>5</v>
+        <v>115</v>
       </c>
       <c r="I263">
-        <v>21759259</v>
+        <v>828752973</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E264">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="F264">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G264">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H264">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="I264">
-        <v>146634259</v>
+        <v>372325888</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -10154,129 +10154,1091 @@
         </is>
       </c>
       <c r="E265">
+        <v>34</v>
+      </c>
+      <c r="F265">
         <v>2</v>
       </c>
-      <c r="F265">
-        <v>1</v>
-      </c>
       <c r="G265">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H265">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="I265">
-        <v>3139879</v>
+        <v>300949073</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E266">
-        <v>5</v>
+        <v>235</v>
       </c>
       <c r="F266">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G266">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H266">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="I266">
-        <v>12870369</v>
+        <v>1293811423</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E267">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="F267">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G267">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H267">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="I267">
-        <v>11180000</v>
+        <v>296596296</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>NBH</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Chưa map wms</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="E268">
+        <v>74</v>
+      </c>
+      <c r="F268">
+        <v>5</v>
+      </c>
+      <c r="G268">
+        <v>5</v>
+      </c>
+      <c r="H268">
+        <v>74</v>
+      </c>
+      <c r="I268">
+        <v>588722955</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>PTO</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Chưa map wms</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="E269">
+        <v>262</v>
+      </c>
+      <c r="F269">
+        <v>11</v>
+      </c>
+      <c r="G269">
+        <v>10</v>
+      </c>
+      <c r="H269">
+        <v>228</v>
+      </c>
+      <c r="I269">
+        <v>2139006768</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>PTO</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Chưa map wms</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Chờ hàng CNCT</t>
+        </is>
+      </c>
+      <c r="E270">
+        <v>22</v>
+      </c>
+      <c r="F270">
+        <v>1</v>
+      </c>
+      <c r="G270">
+        <v>1</v>
+      </c>
+      <c r="H270">
+        <v>22</v>
+      </c>
+      <c r="I270">
+        <v>81888888</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>PTO</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Chưa map wms</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Đang thực hiện</t>
+        </is>
+      </c>
+      <c r="E271">
+        <v>17</v>
+      </c>
+      <c r="F271">
+        <v>1</v>
+      </c>
+      <c r="G271">
+        <v>1</v>
+      </c>
+      <c r="H271">
+        <v>17</v>
+      </c>
+      <c r="I271">
+        <v>129629629</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>QNI</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Chưa map wms</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="E272">
+        <v>152</v>
+      </c>
+      <c r="F272">
+        <v>9</v>
+      </c>
+      <c r="G272">
+        <v>7</v>
+      </c>
+      <c r="H272">
+        <v>120</v>
+      </c>
+      <c r="I272">
+        <v>1055740737</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>QNI</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Chưa map wms</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Đang thực hiện</t>
+        </is>
+      </c>
+      <c r="E273">
+        <v>18</v>
+      </c>
+      <c r="F273">
+        <v>1</v>
+      </c>
+      <c r="G273">
+        <v>1</v>
+      </c>
+      <c r="H273">
+        <v>18</v>
+      </c>
+      <c r="I273">
+        <v>139768518</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>QTI</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Chưa map wms</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="E274">
+        <v>26</v>
+      </c>
+      <c r="F274">
+        <v>2</v>
+      </c>
+      <c r="G274">
+        <v>2</v>
+      </c>
+      <c r="H274">
+        <v>26</v>
+      </c>
+      <c r="I274">
+        <v>254242086</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>THA</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Chưa map wms</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="E275">
+        <v>38</v>
+      </c>
+      <c r="F275">
+        <v>2</v>
+      </c>
+      <c r="G275">
+        <v>2</v>
+      </c>
+      <c r="H275">
+        <v>38</v>
+      </c>
+      <c r="I275">
+        <v>284999999</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>THA</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Chưa map wms</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Đang thực hiện</t>
+        </is>
+      </c>
+      <c r="E276">
+        <v>20</v>
+      </c>
+      <c r="F276">
+        <v>1</v>
+      </c>
+      <c r="G276">
+        <v>1</v>
+      </c>
+      <c r="H276">
+        <v>20</v>
+      </c>
+      <c r="I276">
+        <v>146887037</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>TNH</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Chưa map wms</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="E277">
+        <v>140</v>
+      </c>
+      <c r="F277">
+        <v>12</v>
+      </c>
+      <c r="G277">
+        <v>10</v>
+      </c>
+      <c r="H277">
+        <v>112</v>
+      </c>
+      <c r="I277">
+        <v>1380296950</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>TNH</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Chưa map wms</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Miss</t>
+        </is>
+      </c>
+      <c r="E278">
+        <v>24</v>
+      </c>
+      <c r="F278">
+        <v>2</v>
+      </c>
+      <c r="G278">
+        <v>0</v>
+      </c>
+      <c r="H278">
+        <v>0</v>
+      </c>
+      <c r="I278">
+        <v>92907407</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>TNH</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Chưa map wms</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Đang thực hiện</t>
+        </is>
+      </c>
+      <c r="E279">
+        <v>10</v>
+      </c>
+      <c r="F279">
+        <v>1</v>
+      </c>
+      <c r="G279">
+        <v>1</v>
+      </c>
+      <c r="H279">
+        <v>10</v>
+      </c>
+      <c r="I279">
+        <v>107407407</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>TQG</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Chưa map wms</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="E280">
+        <v>110</v>
+      </c>
+      <c r="F280">
+        <v>9</v>
+      </c>
+      <c r="G280">
+        <v>8</v>
+      </c>
+      <c r="H280">
+        <v>98</v>
+      </c>
+      <c r="I280">
+        <v>929231107</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>TTH</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Chưa map wms</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="E281">
+        <v>144</v>
+      </c>
+      <c r="F281">
+        <v>14</v>
+      </c>
+      <c r="G281">
+        <v>14</v>
+      </c>
+      <c r="H281">
+        <v>144</v>
+      </c>
+      <c r="I281">
+        <v>1499900786</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>TTH</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Chưa map wms</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Miss</t>
+        </is>
+      </c>
+      <c r="E282">
+        <v>42</v>
+      </c>
+      <c r="F282">
+        <v>3</v>
+      </c>
+      <c r="G282">
+        <v>3</v>
+      </c>
+      <c r="H282">
+        <v>42</v>
+      </c>
+      <c r="I282">
+        <v>377858795</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>TTH</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Chưa map wms</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Đang thực hiện</t>
+        </is>
+      </c>
+      <c r="E283">
+        <v>12</v>
+      </c>
+      <c r="F283">
+        <v>1</v>
+      </c>
+      <c r="G283">
+        <v>1</v>
+      </c>
+      <c r="H283">
+        <v>12</v>
+      </c>
+      <c r="I283">
+        <v>127777777</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>VLG</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Chưa map wms</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="E284">
+        <v>248</v>
+      </c>
+      <c r="F284">
+        <v>17</v>
+      </c>
+      <c r="G284">
+        <v>16</v>
+      </c>
+      <c r="H284">
+        <v>240</v>
+      </c>
+      <c r="I284">
+        <v>2198066137</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>VLG</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Chưa map wms</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Chờ ký PLHĐ</t>
+        </is>
+      </c>
+      <c r="E285">
+        <v>10</v>
+      </c>
+      <c r="F285">
+        <v>1</v>
+      </c>
+      <c r="G285">
+        <v>1</v>
+      </c>
+      <c r="H285">
+        <v>10</v>
+      </c>
+      <c r="I285">
+        <v>113333333</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>VLG</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Chưa map wms</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Đang thực hiện</t>
+        </is>
+      </c>
+      <c r="E286">
+        <v>56</v>
+      </c>
+      <c r="F286">
+        <v>5</v>
+      </c>
+      <c r="G286">
+        <v>4</v>
+      </c>
+      <c r="H286">
+        <v>24</v>
+      </c>
+      <c r="I286">
+        <v>330625046</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
           <t>TCT_Pin khác</t>
         </is>
       </c>
-      <c r="B268" t="inlineStr">
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>DTP</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Chưa map wms</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="E287">
+        <v>44</v>
+      </c>
+      <c r="F287">
+        <v>2</v>
+      </c>
+      <c r="G287">
+        <v>2</v>
+      </c>
+      <c r="H287">
+        <v>44</v>
+      </c>
+      <c r="I287">
+        <v>342663644</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>TCT_Pin khác</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>GLI</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Chưa map wms</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="E288">
+        <v>30</v>
+      </c>
+      <c r="F288">
+        <v>1</v>
+      </c>
+      <c r="G288">
+        <v>1</v>
+      </c>
+      <c r="H288">
+        <v>30</v>
+      </c>
+      <c r="I288">
+        <v>85400000</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>TCT_Pin khác</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>GLI</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Chưa map wms</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Chờ ký PLHĐ</t>
+        </is>
+      </c>
+      <c r="E289">
+        <v>5</v>
+      </c>
+      <c r="F289">
+        <v>1</v>
+      </c>
+      <c r="G289">
+        <v>1</v>
+      </c>
+      <c r="H289">
+        <v>5</v>
+      </c>
+      <c r="I289">
+        <v>21759259</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>TCT_Pin khác</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>GLI</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Chưa map wms</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Miss</t>
+        </is>
+      </c>
+      <c r="E290">
+        <v>38</v>
+      </c>
+      <c r="F290">
+        <v>3</v>
+      </c>
+      <c r="G290">
+        <v>1</v>
+      </c>
+      <c r="H290">
+        <v>17</v>
+      </c>
+      <c r="I290">
+        <v>146634259</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>TCT_Pin khác</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>HPG</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Chưa map wms</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="E291">
+        <v>2</v>
+      </c>
+      <c r="F291">
+        <v>1</v>
+      </c>
+      <c r="G291">
+        <v>0</v>
+      </c>
+      <c r="H291">
+        <v>0</v>
+      </c>
+      <c r="I291">
+        <v>3139879</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>TCT_Pin khác</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>HPG</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Đã map wms</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Đang thực hiện</t>
+        </is>
+      </c>
+      <c r="E292">
+        <v>5</v>
+      </c>
+      <c r="F292">
+        <v>2</v>
+      </c>
+      <c r="G292">
+        <v>0</v>
+      </c>
+      <c r="H292">
+        <v>0</v>
+      </c>
+      <c r="I292">
+        <v>12870369</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>TCT_Pin khác</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>PTO</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Đã map wms</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>Đang thực hiện</t>
+        </is>
+      </c>
+      <c r="E293">
+        <v>6</v>
+      </c>
+      <c r="F293">
+        <v>1</v>
+      </c>
+      <c r="G293">
+        <v>0</v>
+      </c>
+      <c r="H293">
+        <v>0</v>
+      </c>
+      <c r="I293">
+        <v>11180000</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>TCT_Pin khác</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
         <is>
           <t>QNH</t>
         </is>
       </c>
-      <c r="C268" t="inlineStr">
-        <is>
-          <t>Chưa map wms</t>
-        </is>
-      </c>
-      <c r="D268" t="inlineStr">
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Chưa map wms</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
         <is>
           <t>Đang thực hiện</t>
         </is>
       </c>
-      <c r="E268">
+      <c r="E294">
         <v>10</v>
       </c>
-      <c r="F268">
-        <v>1</v>
-      </c>
-      <c r="G268">
+      <c r="F294">
+        <v>1</v>
+      </c>
+      <c r="G294">
         <v>0</v>
       </c>
-      <c r="H268">
+      <c r="H294">
         <v>0</v>
       </c>
-      <c r="I268">
+      <c r="I294">
         <v>113461215</v>
       </c>
     </row>

--- a/data/nv_aio_bc.xlsx
+++ b/data/nv_aio_bc.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I349"/>
+  <dimension ref="A1:I352"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -540,10 +540,10 @@
         <v>6</v>
       </c>
       <c r="G5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H5">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="I5">
         <v>963552552</v>
@@ -1640,23 +1640,23 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Chờ ký PLHĐ</t>
         </is>
       </c>
       <c r="E35">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="F35">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G35">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H35">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I35">
-        <v>898359256</v>
+        <v>221764814</v>
       </c>
     </row>
     <row r="36">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1677,23 +1677,23 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E36">
-        <v>2</v>
+        <v>67</v>
       </c>
       <c r="F36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G36">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H36">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="I36">
-        <v>4629629</v>
+        <v>676594442</v>
       </c>
     </row>
     <row r="37">
@@ -1714,23 +1714,23 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E37">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="F37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G37">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H37">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I37">
-        <v>381787943</v>
+        <v>4629629</v>
       </c>
     </row>
     <row r="38">
@@ -1741,7 +1741,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1751,23 +1751,23 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E38">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="F38">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G38">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H38">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="I38">
-        <v>614917590</v>
+        <v>381787943</v>
       </c>
     </row>
     <row r="39">
@@ -1788,23 +1788,23 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Chờ ký PLHĐ</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E39">
-        <v>25</v>
+        <v>85</v>
       </c>
       <c r="F39">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G39">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H39">
-        <v>25</v>
+        <v>85</v>
       </c>
       <c r="I39">
-        <v>164574768</v>
+        <v>614917590</v>
       </c>
     </row>
     <row r="40">
@@ -1829,19 +1829,19 @@
         </is>
       </c>
       <c r="E40">
-        <v>135</v>
+        <v>160</v>
       </c>
       <c r="F40">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G40">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H40">
-        <v>135</v>
+        <v>160</v>
       </c>
       <c r="I40">
-        <v>1020745367</v>
+        <v>1185320135</v>
       </c>
     </row>
     <row r="41">
@@ -2121,23 +2121,23 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Chờ ký PLHĐ</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E48">
-        <v>10</v>
+        <v>260</v>
       </c>
       <c r="F48">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G48">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H48">
-        <v>10</v>
+        <v>260</v>
       </c>
       <c r="I48">
-        <v>116212000</v>
+        <v>1305312720</v>
       </c>
     </row>
     <row r="49">
@@ -2158,23 +2158,23 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E49">
-        <v>260</v>
+        <v>39</v>
       </c>
       <c r="F49">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G49">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H49">
-        <v>260</v>
+        <v>39</v>
       </c>
       <c r="I49">
-        <v>1305312720</v>
+        <v>390203200</v>
       </c>
     </row>
     <row r="50">
@@ -2190,28 +2190,28 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E50">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="F50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H50">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="I50">
-        <v>390203200</v>
+        <v>264433607</v>
       </c>
     </row>
     <row r="51">
@@ -2232,23 +2232,23 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E51">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="F51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H51">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="I51">
-        <v>264433607</v>
+        <v>171065000</v>
       </c>
     </row>
     <row r="52">
@@ -2259,33 +2259,33 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E52">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="F52">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G52">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H52">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="I52">
-        <v>171065000</v>
+        <v>375434413</v>
       </c>
     </row>
     <row r="53">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2310,19 +2310,19 @@
         </is>
       </c>
       <c r="E53">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="F53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H53">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="I53">
-        <v>375434413</v>
+        <v>283343703</v>
       </c>
     </row>
     <row r="54">
@@ -2333,33 +2333,33 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E54">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="F54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H54">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="I54">
-        <v>283343703</v>
+        <v>44587962</v>
       </c>
     </row>
     <row r="55">
@@ -2380,11 +2380,11 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E55">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F55">
         <v>1</v>
@@ -2393,10 +2393,10 @@
         <v>1</v>
       </c>
       <c r="H55">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="I55">
-        <v>44587962</v>
+        <v>120370370</v>
       </c>
     </row>
     <row r="56">
@@ -2407,7 +2407,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2417,23 +2417,23 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E56">
-        <v>14</v>
+        <v>172</v>
       </c>
       <c r="F56">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G56">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H56">
-        <v>14</v>
+        <v>172</v>
       </c>
       <c r="I56">
-        <v>120370370</v>
+        <v>906081387</v>
       </c>
     </row>
     <row r="57">
@@ -2454,23 +2454,23 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E57">
-        <v>172</v>
+        <v>58</v>
       </c>
       <c r="F57">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G57">
         <v>3</v>
       </c>
       <c r="H57">
-        <v>172</v>
+        <v>52</v>
       </c>
       <c r="I57">
-        <v>906081387</v>
+        <v>444863701</v>
       </c>
     </row>
     <row r="58">
@@ -2491,23 +2491,23 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E58">
-        <v>58</v>
+        <v>5</v>
       </c>
       <c r="F58">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G58">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H58">
-        <v>52</v>
+        <v>5</v>
       </c>
       <c r="I58">
-        <v>444863701</v>
+        <v>11574074</v>
       </c>
     </row>
     <row r="59">
@@ -2523,16 +2523,16 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E59">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="F59">
         <v>1</v>
@@ -2541,10 +2541,10 @@
         <v>1</v>
       </c>
       <c r="H59">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I59">
-        <v>11574074</v>
+        <v>60000000</v>
       </c>
     </row>
     <row r="60">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2569,7 +2569,7 @@
         </is>
       </c>
       <c r="E60">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F60">
         <v>1</v>
@@ -2578,10 +2578,10 @@
         <v>1</v>
       </c>
       <c r="H60">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I60">
-        <v>60000000</v>
+        <v>100000000</v>
       </c>
     </row>
     <row r="61">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E61">
@@ -2618,7 +2618,7 @@
         <v>10</v>
       </c>
       <c r="I61">
-        <v>100000000</v>
+        <v>63435185</v>
       </c>
     </row>
     <row r="62">
@@ -2629,21 +2629,21 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E62">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F62">
         <v>1</v>
@@ -2652,10 +2652,10 @@
         <v>1</v>
       </c>
       <c r="H62">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="I62">
-        <v>63435185</v>
+        <v>201388888</v>
       </c>
     </row>
     <row r="63">
@@ -2666,21 +2666,21 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E63">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F63">
         <v>1</v>
@@ -2689,10 +2689,10 @@
         <v>1</v>
       </c>
       <c r="H63">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I63">
-        <v>201388888</v>
+        <v>195277777</v>
       </c>
     </row>
     <row r="64">
@@ -2713,11 +2713,11 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E64">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="F64">
         <v>1</v>
@@ -2726,10 +2726,10 @@
         <v>1</v>
       </c>
       <c r="H64">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="I64">
-        <v>195277777</v>
+        <v>388888888</v>
       </c>
     </row>
     <row r="65">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2750,23 +2750,23 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E65">
-        <v>44</v>
+        <v>174</v>
       </c>
       <c r="F65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H65">
-        <v>44</v>
+        <v>174</v>
       </c>
       <c r="I65">
-        <v>388888888</v>
+        <v>806204628</v>
       </c>
     </row>
     <row r="66">
@@ -2787,23 +2787,23 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Chờ hàng CNCT</t>
         </is>
       </c>
       <c r="E66">
-        <v>174</v>
+        <v>2</v>
       </c>
       <c r="F66">
         <v>2</v>
       </c>
       <c r="G66">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H66">
-        <v>174</v>
+        <v>0</v>
       </c>
       <c r="I66">
-        <v>806204628</v>
+        <v>3611110</v>
       </c>
     </row>
     <row r="67">
@@ -2824,23 +2824,23 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Chờ hàng CNCT</t>
+          <t>Chờ ký PLHĐ</t>
         </is>
       </c>
       <c r="E67">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="F67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H67">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I67">
-        <v>3611110</v>
+        <v>136805555</v>
       </c>
     </row>
     <row r="68">
@@ -2865,19 +2865,19 @@
         </is>
       </c>
       <c r="E68">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="F68">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G68">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H68">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="I68">
-        <v>1216424942</v>
+        <v>1079619387</v>
       </c>
     </row>
     <row r="69">
@@ -3272,10 +3272,10 @@
         </is>
       </c>
       <c r="E79">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G79">
         <v>1</v>
@@ -3284,7 +3284,7 @@
         <v>15</v>
       </c>
       <c r="I79">
-        <v>223888888</v>
+        <v>106018518</v>
       </c>
     </row>
     <row r="80">
@@ -3309,19 +3309,19 @@
         </is>
       </c>
       <c r="E80">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="F80">
+        <v>7</v>
+      </c>
+      <c r="G80">
         <v>6</v>
       </c>
-      <c r="G80">
-        <v>4</v>
-      </c>
       <c r="H80">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="I80">
-        <v>1091791664</v>
+        <v>1164939812</v>
       </c>
     </row>
     <row r="81">
@@ -3346,19 +3346,19 @@
         </is>
       </c>
       <c r="E81">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="F81">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G81">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H81">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="I81">
-        <v>60185185</v>
+        <v>178055555</v>
       </c>
     </row>
     <row r="82">
@@ -3416,11 +3416,11 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Chờ ký PLHĐ</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E83">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F83">
         <v>1</v>
@@ -3429,10 +3429,10 @@
         <v>1</v>
       </c>
       <c r="H83">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="I83">
-        <v>66666666</v>
+        <v>155555555</v>
       </c>
     </row>
     <row r="84">
@@ -3453,23 +3453,23 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E84">
-        <v>18</v>
+        <v>97</v>
       </c>
       <c r="F84">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G84">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H84">
-        <v>18</v>
+        <v>97</v>
       </c>
       <c r="I84">
-        <v>155555555</v>
+        <v>569037035</v>
       </c>
     </row>
     <row r="85">
@@ -3480,33 +3480,33 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E85">
-        <v>97</v>
+        <v>12</v>
       </c>
       <c r="F85">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G85">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H85">
-        <v>97</v>
+        <v>12</v>
       </c>
       <c r="I85">
-        <v>569037035</v>
+        <v>99816222</v>
       </c>
     </row>
     <row r="86">
@@ -3527,11 +3527,11 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E86">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F86">
         <v>1</v>
@@ -3540,10 +3540,10 @@
         <v>1</v>
       </c>
       <c r="H86">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I86">
-        <v>99816222</v>
+        <v>65326511</v>
       </c>
     </row>
     <row r="87">
@@ -3554,7 +3554,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3564,23 +3564,23 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E87">
-        <v>6</v>
+        <v>52</v>
       </c>
       <c r="F87">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G87">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H87">
-        <v>6</v>
+        <v>52</v>
       </c>
       <c r="I87">
-        <v>65326511</v>
+        <v>183614814</v>
       </c>
     </row>
     <row r="88">
@@ -3601,23 +3601,23 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E88">
-        <v>62</v>
+        <v>287</v>
       </c>
       <c r="F88">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G88">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H88">
-        <v>62</v>
+        <v>287</v>
       </c>
       <c r="I88">
-        <v>245164814</v>
+        <v>1459692589</v>
       </c>
     </row>
     <row r="89">
@@ -3638,23 +3638,23 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E89">
-        <v>287</v>
+        <v>10</v>
       </c>
       <c r="F89">
+        <v>1</v>
+      </c>
+      <c r="G89">
+        <v>1</v>
+      </c>
+      <c r="H89">
         <v>10</v>
       </c>
-      <c r="G89">
-        <v>10</v>
-      </c>
-      <c r="H89">
-        <v>287</v>
-      </c>
       <c r="I89">
-        <v>1459692589</v>
+        <v>61550000</v>
       </c>
     </row>
     <row r="90">
@@ -3753,19 +3753,19 @@
         </is>
       </c>
       <c r="E92">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="F92">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G92">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H92">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="I92">
-        <v>351166849</v>
+        <v>250240924</v>
       </c>
     </row>
     <row r="93">
@@ -3864,19 +3864,19 @@
         </is>
       </c>
       <c r="E95">
-        <v>216</v>
+        <v>164</v>
       </c>
       <c r="F95">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G95">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H95">
-        <v>186</v>
+        <v>134</v>
       </c>
       <c r="I95">
-        <v>1764466105</v>
+        <v>1425577217</v>
       </c>
     </row>
     <row r="96">
@@ -3897,23 +3897,23 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Chờ ký PLHĐ</t>
         </is>
       </c>
       <c r="E96">
-        <v>377</v>
+        <v>12</v>
       </c>
       <c r="F96">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G96">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="H96">
-        <v>263</v>
+        <v>12</v>
       </c>
       <c r="I96">
-        <v>2563740582</v>
+        <v>95231481</v>
       </c>
     </row>
     <row r="97">
@@ -3934,23 +3934,23 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E97">
-        <v>140</v>
+        <v>365</v>
       </c>
       <c r="F97">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="G97">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H97">
-        <v>36</v>
+        <v>251</v>
       </c>
       <c r="I97">
-        <v>850099546</v>
+        <v>2508323915</v>
       </c>
     </row>
     <row r="98">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3975,19 +3975,19 @@
         </is>
       </c>
       <c r="E98">
-        <v>64</v>
+        <v>140</v>
       </c>
       <c r="F98">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G98">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H98">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="I98">
-        <v>362060184</v>
+        <v>850099546</v>
       </c>
     </row>
     <row r="99">
@@ -3998,33 +3998,33 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>CBG</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E99">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="F99">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G99">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H99">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="I99">
-        <v>342047091</v>
+        <v>362060184</v>
       </c>
     </row>
     <row r="100">
@@ -4045,23 +4045,23 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E100">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="F100">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G100">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H100">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="I100">
-        <v>138171055</v>
+        <v>342047091</v>
       </c>
     </row>
     <row r="101">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>CBG</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4082,23 +4082,23 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E101">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="F101">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G101">
         <v>1</v>
       </c>
       <c r="H101">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="I101">
-        <v>303708413</v>
+        <v>138171055</v>
       </c>
     </row>
     <row r="102">
@@ -4119,11 +4119,11 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Chờ ký PLHĐ</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E102">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F102">
         <v>1</v>
@@ -4132,10 +4132,10 @@
         <v>1</v>
       </c>
       <c r="H102">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I102">
-        <v>64814814</v>
+        <v>51076979</v>
       </c>
     </row>
     <row r="103">
@@ -4156,23 +4156,23 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Chờ ký PLHĐ</t>
         </is>
       </c>
       <c r="E103">
-        <v>310</v>
+        <v>20</v>
       </c>
       <c r="F103">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="G103">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="H103">
-        <v>294</v>
+        <v>20</v>
       </c>
       <c r="I103">
-        <v>2368245549</v>
+        <v>169444443</v>
       </c>
     </row>
     <row r="104">
@@ -4193,23 +4193,23 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E104">
-        <v>80</v>
+        <v>298</v>
       </c>
       <c r="F104">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G104">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="H104">
-        <v>80</v>
+        <v>282</v>
       </c>
       <c r="I104">
-        <v>677037035</v>
+        <v>2263615920</v>
       </c>
     </row>
     <row r="105">
@@ -4225,7 +4225,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -4234,19 +4234,19 @@
         </is>
       </c>
       <c r="E105">
-        <v>8</v>
+        <v>80</v>
       </c>
       <c r="F105">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G105">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H105">
-        <v>8</v>
+        <v>80</v>
       </c>
       <c r="I105">
-        <v>109937325</v>
+        <v>677037035</v>
       </c>
     </row>
     <row r="106">
@@ -4257,21 +4257,21 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E106">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F106">
         <v>1</v>
@@ -4280,10 +4280,10 @@
         <v>1</v>
       </c>
       <c r="H106">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="I106">
-        <v>152777777</v>
+        <v>109937325</v>
       </c>
     </row>
     <row r="107">
@@ -4304,23 +4304,23 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E107">
-        <v>141</v>
+        <v>26</v>
       </c>
       <c r="F107">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G107">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H107">
-        <v>86</v>
+        <v>26</v>
       </c>
       <c r="I107">
-        <v>1140562377</v>
+        <v>152777777</v>
       </c>
     </row>
     <row r="108">
@@ -4341,23 +4341,23 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E108">
-        <v>32</v>
+        <v>141</v>
       </c>
       <c r="F108">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G108">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H108">
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="I108">
-        <v>208889814</v>
+        <v>1140562377</v>
       </c>
     </row>
     <row r="109">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>DBN</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4378,11 +4378,11 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Chờ ký PLHĐ</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E109">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="F109">
         <v>1</v>
@@ -4391,10 +4391,10 @@
         <v>1</v>
       </c>
       <c r="H109">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="I109">
-        <v>104629629</v>
+        <v>208889814</v>
       </c>
     </row>
     <row r="110">
@@ -4415,11 +4415,11 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Chờ ký PLHĐ</t>
         </is>
       </c>
       <c r="E110">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F110">
         <v>1</v>
@@ -4428,10 +4428,10 @@
         <v>1</v>
       </c>
       <c r="H110">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I110">
-        <v>120740740</v>
+        <v>104629629</v>
       </c>
     </row>
     <row r="111">
@@ -4456,19 +4456,19 @@
         </is>
       </c>
       <c r="E111">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="F111">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G111">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H111">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="I111">
-        <v>307249999</v>
+        <v>427990739</v>
       </c>
     </row>
     <row r="112">
@@ -4530,19 +4530,19 @@
         </is>
       </c>
       <c r="E113">
-        <v>198</v>
+        <v>254</v>
       </c>
       <c r="F113">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G113">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H113">
-        <v>190</v>
+        <v>230</v>
       </c>
       <c r="I113">
-        <v>1172331347</v>
+        <v>1630368375</v>
       </c>
     </row>
     <row r="114">
@@ -4641,7 +4641,7 @@
         </is>
       </c>
       <c r="E116">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="F116">
         <v>6</v>
@@ -4650,10 +4650,10 @@
         <v>6</v>
       </c>
       <c r="H116">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="I116">
-        <v>762623146</v>
+        <v>814706480</v>
       </c>
     </row>
     <row r="117">
@@ -4678,7 +4678,7 @@
         </is>
       </c>
       <c r="E117">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="F117">
         <v>35</v>
@@ -4687,10 +4687,10 @@
         <v>33</v>
       </c>
       <c r="H117">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="I117">
-        <v>4710329854</v>
+        <v>4658246520</v>
       </c>
     </row>
     <row r="118">
@@ -4715,19 +4715,19 @@
         </is>
       </c>
       <c r="E118">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="F118">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G118">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H118">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="I118">
-        <v>288009259</v>
+        <v>185185185</v>
       </c>
     </row>
     <row r="119">
@@ -4752,19 +4752,19 @@
         </is>
       </c>
       <c r="E119">
-        <v>148</v>
+        <v>90</v>
       </c>
       <c r="F119">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G119">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H119">
-        <v>148</v>
+        <v>90</v>
       </c>
       <c r="I119">
-        <v>1118694603</v>
+        <v>716503820</v>
       </c>
     </row>
     <row r="120">
@@ -4789,19 +4789,19 @@
         </is>
       </c>
       <c r="E120">
-        <v>12</v>
+        <v>77</v>
       </c>
       <c r="F120">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G120">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H120">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="I120">
-        <v>103240740</v>
+        <v>535648146</v>
       </c>
     </row>
     <row r="121">
@@ -4826,19 +4826,19 @@
         </is>
       </c>
       <c r="E121">
-        <v>710</v>
+        <v>673</v>
       </c>
       <c r="F121">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G121">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H121">
-        <v>460</v>
+        <v>427</v>
       </c>
       <c r="I121">
-        <v>5350069510</v>
+        <v>5120947661</v>
       </c>
     </row>
     <row r="122">
@@ -4863,19 +4863,19 @@
         </is>
       </c>
       <c r="E122">
-        <v>153</v>
+        <v>177</v>
       </c>
       <c r="F122">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G122">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H122">
-        <v>153</v>
+        <v>177</v>
       </c>
       <c r="I122">
-        <v>1216556280</v>
+        <v>1421900643</v>
       </c>
     </row>
     <row r="123">
@@ -4900,19 +4900,19 @@
         </is>
       </c>
       <c r="E123">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="F123">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G123">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H123">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="I123">
-        <v>1141762953</v>
+        <v>941444443</v>
       </c>
     </row>
     <row r="124">
@@ -4937,19 +4937,19 @@
         </is>
       </c>
       <c r="E124">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="F124">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G124">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H124">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="I124">
-        <v>1782439190</v>
+        <v>1900957708</v>
       </c>
     </row>
     <row r="125">
@@ -4974,7 +4974,7 @@
         </is>
       </c>
       <c r="E125">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="F125">
         <v>4</v>
@@ -4983,10 +4983,10 @@
         <v>4</v>
       </c>
       <c r="H125">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="I125">
-        <v>731434404</v>
+        <v>760857637</v>
       </c>
     </row>
     <row r="126">
@@ -5270,19 +5270,19 @@
         </is>
       </c>
       <c r="E133">
-        <v>259</v>
+        <v>294</v>
       </c>
       <c r="F133">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G133">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H133">
-        <v>245</v>
+        <v>280</v>
       </c>
       <c r="I133">
-        <v>2212681492</v>
+        <v>2596385195</v>
       </c>
     </row>
     <row r="134">
@@ -5344,19 +5344,19 @@
         </is>
       </c>
       <c r="E135">
-        <v>1303</v>
+        <v>1366</v>
       </c>
       <c r="F135">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G135">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H135">
-        <v>1219</v>
+        <v>1196</v>
       </c>
       <c r="I135">
-        <v>10478575674</v>
+        <v>10591640892</v>
       </c>
     </row>
     <row r="136">
@@ -5566,19 +5566,19 @@
         </is>
       </c>
       <c r="E141">
-        <v>146</v>
+        <v>89</v>
       </c>
       <c r="F141">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G141">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H141">
-        <v>146</v>
+        <v>89</v>
       </c>
       <c r="I141">
-        <v>1364099541</v>
+        <v>855400851</v>
       </c>
     </row>
     <row r="142">
@@ -5603,19 +5603,19 @@
         </is>
       </c>
       <c r="E142">
-        <v>548</v>
+        <v>563</v>
       </c>
       <c r="F142">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G142">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H142">
-        <v>501</v>
+        <v>516</v>
       </c>
       <c r="I142">
-        <v>4380334850</v>
+        <v>4523167700</v>
       </c>
     </row>
     <row r="143">
@@ -5636,23 +5636,23 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Chờ ký PLHĐ</t>
         </is>
       </c>
       <c r="E143">
-        <v>119</v>
+        <v>22</v>
       </c>
       <c r="F143">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G143">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H143">
-        <v>119</v>
+        <v>22</v>
       </c>
       <c r="I143">
-        <v>955600080</v>
+        <v>201388888</v>
       </c>
     </row>
     <row r="144">
@@ -5673,23 +5673,23 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E144">
-        <v>14</v>
+        <v>97</v>
       </c>
       <c r="F144">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G144">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H144">
-        <v>14</v>
+        <v>97</v>
       </c>
       <c r="I144">
-        <v>163291350</v>
+        <v>754211192</v>
       </c>
     </row>
     <row r="145">
@@ -5700,33 +5700,33 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E145">
-        <v>135</v>
+        <v>14</v>
       </c>
       <c r="F145">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G145">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H145">
-        <v>135</v>
+        <v>14</v>
       </c>
       <c r="I145">
-        <v>1173360984</v>
+        <v>163291350</v>
       </c>
     </row>
     <row r="146">
@@ -5747,23 +5747,23 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Chờ ký PLHĐ</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E146">
-        <v>16</v>
+        <v>135</v>
       </c>
       <c r="F146">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G146">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H146">
-        <v>16</v>
+        <v>135</v>
       </c>
       <c r="I146">
-        <v>134259259</v>
+        <v>1173360984</v>
       </c>
     </row>
     <row r="147">
@@ -5784,23 +5784,23 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Chờ ký PLHĐ</t>
         </is>
       </c>
       <c r="E147">
-        <v>699</v>
+        <v>16</v>
       </c>
       <c r="F147">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="G147">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="H147">
-        <v>655</v>
+        <v>16</v>
       </c>
       <c r="I147">
-        <v>5178545883</v>
+        <v>134259259</v>
       </c>
     </row>
     <row r="148">
@@ -5821,23 +5821,23 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E148">
-        <v>16</v>
+        <v>711</v>
       </c>
       <c r="F148">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="G148">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="H148">
-        <v>16</v>
+        <v>655</v>
       </c>
       <c r="I148">
-        <v>54629629</v>
+        <v>5297064401</v>
       </c>
     </row>
     <row r="149">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -5862,19 +5862,19 @@
         </is>
       </c>
       <c r="E149">
-        <v>68</v>
+        <v>16</v>
       </c>
       <c r="F149">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G149">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H149">
-        <v>68</v>
+        <v>16</v>
       </c>
       <c r="I149">
-        <v>412456317</v>
+        <v>54629629</v>
       </c>
     </row>
     <row r="150">
@@ -5885,33 +5885,33 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Chờ ký PLHĐ</t>
         </is>
       </c>
       <c r="E150">
-        <v>58</v>
+        <v>16</v>
       </c>
       <c r="F150">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G150">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H150">
-        <v>58</v>
+        <v>16</v>
       </c>
       <c r="I150">
-        <v>504496294</v>
+        <v>134537037</v>
       </c>
     </row>
     <row r="151">
@@ -5922,33 +5922,33 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E151">
-        <v>396</v>
+        <v>52</v>
       </c>
       <c r="F151">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="G151">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="H151">
-        <v>384</v>
+        <v>52</v>
       </c>
       <c r="I151">
-        <v>3544409855</v>
+        <v>277919280</v>
       </c>
     </row>
     <row r="152">
@@ -5969,23 +5969,23 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E152">
-        <v>126</v>
+        <v>58</v>
       </c>
       <c r="F152">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G152">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H152">
-        <v>126</v>
+        <v>58</v>
       </c>
       <c r="I152">
-        <v>1142289809</v>
+        <v>504496294</v>
       </c>
     </row>
     <row r="153">
@@ -6001,28 +6001,28 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E153">
-        <v>12</v>
+        <v>396</v>
       </c>
       <c r="F153">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="G153">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="H153">
-        <v>12</v>
+        <v>384</v>
       </c>
       <c r="I153">
-        <v>125000000</v>
+        <v>3544409855</v>
       </c>
     </row>
     <row r="154">
@@ -6033,7 +6033,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -6043,11 +6043,11 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E154">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F154">
         <v>8</v>
@@ -6056,10 +6056,10 @@
         <v>8</v>
       </c>
       <c r="H154">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="I154">
-        <v>832133987</v>
+        <v>1142289809</v>
       </c>
     </row>
     <row r="155">
@@ -6080,23 +6080,23 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Chờ hàng TTQH</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E155">
-        <v>2</v>
+        <v>248</v>
       </c>
       <c r="F155">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="G155">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="H155">
-        <v>2</v>
+        <v>248</v>
       </c>
       <c r="I155">
-        <v>44907407</v>
+        <v>1696996486</v>
       </c>
     </row>
     <row r="156">
@@ -6117,23 +6117,23 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Chờ ký PLHĐ</t>
+          <t>Chờ hàng TTQH</t>
         </is>
       </c>
       <c r="E156">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="F156">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G156">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H156">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="I156">
-        <v>253215740</v>
+        <v>44907407</v>
       </c>
     </row>
     <row r="157">
@@ -6154,23 +6154,23 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Chờ ký PLHĐ</t>
         </is>
       </c>
       <c r="E157">
-        <v>479</v>
+        <v>19</v>
       </c>
       <c r="F157">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="G157">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="H157">
-        <v>422</v>
+        <v>19</v>
       </c>
       <c r="I157">
-        <v>3902195789</v>
+        <v>124417740</v>
       </c>
     </row>
     <row r="158">
@@ -6191,23 +6191,23 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E158">
-        <v>32</v>
+        <v>307</v>
       </c>
       <c r="F158">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="G158">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="H158">
-        <v>32</v>
+        <v>250</v>
       </c>
       <c r="I158">
-        <v>223630814</v>
+        <v>2735153383</v>
       </c>
     </row>
     <row r="159">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -6228,23 +6228,23 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E159">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="F159">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G159">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H159">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="I159">
-        <v>596652775</v>
+        <v>344143814</v>
       </c>
     </row>
     <row r="160">
@@ -6255,21 +6255,21 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Chờ ký PLHĐ</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E160">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="F160">
         <v>1</v>
@@ -6278,10 +6278,10 @@
         <v>1</v>
       </c>
       <c r="H160">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="I160">
-        <v>102777777</v>
+        <v>143920000</v>
       </c>
     </row>
     <row r="161">
@@ -6302,23 +6302,23 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E161">
-        <v>525</v>
+        <v>64</v>
       </c>
       <c r="F161">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="G161">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="H161">
-        <v>504</v>
+        <v>64</v>
       </c>
       <c r="I161">
-        <v>4524270350</v>
+        <v>596652775</v>
       </c>
     </row>
     <row r="162">
@@ -6339,23 +6339,23 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Chờ ký PLHĐ</t>
         </is>
       </c>
       <c r="E162">
-        <v>130</v>
+        <v>1</v>
       </c>
       <c r="F162">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G162">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H162">
-        <v>130</v>
+        <v>1</v>
       </c>
       <c r="I162">
-        <v>693759258</v>
+        <v>102777777</v>
       </c>
     </row>
     <row r="163">
@@ -6371,28 +6371,28 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E163">
-        <v>20</v>
+        <v>539</v>
       </c>
       <c r="F163">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="G163">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="H163">
-        <v>8</v>
+        <v>512</v>
       </c>
       <c r="I163">
-        <v>178657407</v>
+        <v>4644346275</v>
       </c>
     </row>
     <row r="164">
@@ -6403,7 +6403,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -6413,11 +6413,11 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E164">
-        <v>26</v>
+        <v>118</v>
       </c>
       <c r="F164">
         <v>2</v>
@@ -6426,10 +6426,10 @@
         <v>2</v>
       </c>
       <c r="H164">
-        <v>26</v>
+        <v>118</v>
       </c>
       <c r="I164">
-        <v>235988061</v>
+        <v>587416666</v>
       </c>
     </row>
     <row r="165">
@@ -6440,12 +6440,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -6454,19 +6454,19 @@
         </is>
       </c>
       <c r="E165">
-        <v>357</v>
+        <v>12</v>
       </c>
       <c r="F165">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="G165">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="H165">
-        <v>357</v>
+        <v>12</v>
       </c>
       <c r="I165">
-        <v>2962644564</v>
+        <v>106342592</v>
       </c>
     </row>
     <row r="166">
@@ -6477,21 +6477,21 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>LCU</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Chờ ký PLHĐ</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E166">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F166">
         <v>1</v>
@@ -6503,7 +6503,7 @@
         <v>0</v>
       </c>
       <c r="I166">
-        <v>138888888</v>
+        <v>74074074</v>
       </c>
     </row>
     <row r="167">
@@ -6514,7 +6514,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>LCU</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -6524,23 +6524,23 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E167">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F167">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G167">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H167">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="I167">
-        <v>99986111</v>
+        <v>235988061</v>
       </c>
     </row>
     <row r="168">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>LCU</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -6561,23 +6561,23 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E168">
-        <v>68</v>
+        <v>347</v>
       </c>
       <c r="F168">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="G168">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="H168">
-        <v>36</v>
+        <v>347</v>
       </c>
       <c r="I168">
-        <v>450515740</v>
+        <v>2853991688</v>
       </c>
     </row>
     <row r="169">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>LCU</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -6598,23 +6598,23 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Chờ ký PLHĐ</t>
         </is>
       </c>
       <c r="E169">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="F169">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G169">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H169">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="I169">
-        <v>445117850</v>
+        <v>138888888</v>
       </c>
     </row>
     <row r="170">
@@ -6625,7 +6625,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>LCU</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -6635,11 +6635,11 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Chờ ký PLHĐ</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E170">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F170">
         <v>1</v>
@@ -6648,10 +6648,10 @@
         <v>1</v>
       </c>
       <c r="H170">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="I170">
-        <v>104629629</v>
+        <v>99986111</v>
       </c>
     </row>
     <row r="171">
@@ -6662,7 +6662,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>LCU</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -6672,23 +6672,23 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E171">
-        <v>548</v>
+        <v>68</v>
       </c>
       <c r="F171">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="G171">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="H171">
-        <v>487</v>
+        <v>36</v>
       </c>
       <c r="I171">
-        <v>3981190987</v>
+        <v>450515740</v>
       </c>
     </row>
     <row r="172">
@@ -6709,11 +6709,11 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E172">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F172">
         <v>3</v>
@@ -6722,10 +6722,10 @@
         <v>3</v>
       </c>
       <c r="H172">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I172">
-        <v>165740740</v>
+        <v>339562295</v>
       </c>
     </row>
     <row r="173">
@@ -6741,16 +6741,16 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Chờ ký PLHĐ</t>
         </is>
       </c>
       <c r="E173">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="F173">
         <v>1</v>
@@ -6759,10 +6759,10 @@
         <v>1</v>
       </c>
       <c r="H173">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="I173">
-        <v>137870370</v>
+        <v>104629629</v>
       </c>
     </row>
     <row r="174">
@@ -6778,28 +6778,28 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E174">
-        <v>16</v>
+        <v>560</v>
       </c>
       <c r="F174">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="G174">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="H174">
-        <v>16</v>
+        <v>520</v>
       </c>
       <c r="I174">
-        <v>203888888</v>
+        <v>4046005801</v>
       </c>
     </row>
     <row r="175">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -6820,11 +6820,11 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E175">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="F175">
         <v>3</v>
@@ -6833,10 +6833,10 @@
         <v>3</v>
       </c>
       <c r="H175">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="I175">
-        <v>434210184</v>
+        <v>165740740</v>
       </c>
     </row>
     <row r="176">
@@ -6847,33 +6847,33 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E176">
-        <v>114</v>
+        <v>44</v>
       </c>
       <c r="F176">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G176">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H176">
-        <v>114</v>
+        <v>44</v>
       </c>
       <c r="I176">
-        <v>980439812</v>
+        <v>243425925</v>
       </c>
     </row>
     <row r="177">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -6898,7 +6898,7 @@
         </is>
       </c>
       <c r="E177">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="F177">
         <v>2</v>
@@ -6907,10 +6907,10 @@
         <v>2</v>
       </c>
       <c r="H177">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="I177">
-        <v>255674073</v>
+        <v>203888888</v>
       </c>
     </row>
     <row r="178">
@@ -6921,7 +6921,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -6935,19 +6935,19 @@
         </is>
       </c>
       <c r="E178">
-        <v>383</v>
+        <v>44</v>
       </c>
       <c r="F178">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="G178">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="H178">
-        <v>375</v>
+        <v>44</v>
       </c>
       <c r="I178">
-        <v>3256028799</v>
+        <v>434210184</v>
       </c>
     </row>
     <row r="179">
@@ -6958,7 +6958,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -6968,23 +6968,23 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Chờ hàng CNCT</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E179">
-        <v>6</v>
+        <v>114</v>
       </c>
       <c r="F179">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G179">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H179">
-        <v>6</v>
+        <v>114</v>
       </c>
       <c r="I179">
-        <v>15277777</v>
+        <v>980439812</v>
       </c>
     </row>
     <row r="180">
@@ -6995,7 +6995,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -7005,23 +7005,23 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Chờ ký PLHĐ</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E180">
-        <v>118</v>
+        <v>30</v>
       </c>
       <c r="F180">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G180">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H180">
-        <v>118</v>
+        <v>30</v>
       </c>
       <c r="I180">
-        <v>1074937959</v>
+        <v>255674073</v>
       </c>
     </row>
     <row r="181">
@@ -7042,23 +7042,23 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E181">
-        <v>1886</v>
+        <v>383</v>
       </c>
       <c r="F181">
-        <v>116</v>
+        <v>24</v>
       </c>
       <c r="G181">
-        <v>103</v>
+        <v>23</v>
       </c>
       <c r="H181">
-        <v>1583</v>
+        <v>375</v>
       </c>
       <c r="I181">
-        <v>16406739107</v>
+        <v>3256028799</v>
       </c>
     </row>
     <row r="182">
@@ -7079,23 +7079,23 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Chờ hàng CNCT</t>
         </is>
       </c>
       <c r="E182">
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="F182">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G182">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H182">
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="I182">
-        <v>410741665</v>
+        <v>15277777</v>
       </c>
     </row>
     <row r="183">
@@ -7111,28 +7111,28 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Chờ ký PLHĐ</t>
         </is>
       </c>
       <c r="E183">
-        <v>38</v>
+        <v>118</v>
       </c>
       <c r="F183">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G183">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H183">
-        <v>38</v>
+        <v>118</v>
       </c>
       <c r="I183">
-        <v>422713888</v>
+        <v>1074937959</v>
       </c>
     </row>
     <row r="184">
@@ -7148,28 +7148,28 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E184">
-        <v>24</v>
+        <v>1886</v>
       </c>
       <c r="F184">
-        <v>2</v>
+        <v>116</v>
       </c>
       <c r="G184">
-        <v>2</v>
+        <v>103</v>
       </c>
       <c r="H184">
-        <v>24</v>
+        <v>1583</v>
       </c>
       <c r="I184">
-        <v>247196295</v>
+        <v>16406739107</v>
       </c>
     </row>
     <row r="185">
@@ -7180,7 +7180,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -7190,23 +7190,23 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E185">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F185">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G185">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H185">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I185">
-        <v>404551892</v>
+        <v>410741665</v>
       </c>
     </row>
     <row r="186">
@@ -7217,17 +7217,17 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Chờ ký PLHĐ</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E186">
@@ -7243,7 +7243,7 @@
         <v>28</v>
       </c>
       <c r="I186">
-        <v>227033783</v>
+        <v>327343518</v>
       </c>
     </row>
     <row r="187">
@@ -7254,33 +7254,33 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E187">
-        <v>333</v>
+        <v>24</v>
       </c>
       <c r="F187">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="G187">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="H187">
-        <v>301</v>
+        <v>24</v>
       </c>
       <c r="I187">
-        <v>2564600292</v>
+        <v>247196295</v>
       </c>
     </row>
     <row r="188">
@@ -7301,23 +7301,23 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E188">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="F188">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G188">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H188">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="I188">
-        <v>125935772</v>
+        <v>513070410</v>
       </c>
     </row>
     <row r="189">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Chờ ký PLHĐ</t>
         </is>
       </c>
       <c r="E189">
@@ -7354,7 +7354,7 @@
         <v>16</v>
       </c>
       <c r="I189">
-        <v>135648148</v>
+        <v>141348700</v>
       </c>
     </row>
     <row r="190">
@@ -7365,7 +7365,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -7375,23 +7375,23 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E190">
-        <v>76</v>
+        <v>321</v>
       </c>
       <c r="F190">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="G190">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H190">
-        <v>76</v>
+        <v>289</v>
       </c>
       <c r="I190">
-        <v>487646925</v>
+        <v>2456081774</v>
       </c>
     </row>
     <row r="191">
@@ -7402,7 +7402,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -7412,23 +7412,23 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E191">
-        <v>336</v>
+        <v>16</v>
       </c>
       <c r="F191">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G191">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H191">
-        <v>316</v>
+        <v>16</v>
       </c>
       <c r="I191">
-        <v>2714401935</v>
+        <v>125935772</v>
       </c>
     </row>
     <row r="192">
@@ -7439,12 +7439,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -7453,19 +7453,19 @@
         </is>
       </c>
       <c r="E192">
-        <v>111</v>
+        <v>16</v>
       </c>
       <c r="F192">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G192">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H192">
-        <v>111</v>
+        <v>16</v>
       </c>
       <c r="I192">
-        <v>846229904</v>
+        <v>135648148</v>
       </c>
     </row>
     <row r="193">
@@ -7481,28 +7481,28 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E193">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="F193">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G193">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H193">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="I193">
-        <v>670042361</v>
+        <v>347021925</v>
       </c>
     </row>
     <row r="194">
@@ -7518,28 +7518,28 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E194">
-        <v>375</v>
+        <v>309</v>
       </c>
       <c r="F194">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G194">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="H194">
-        <v>375</v>
+        <v>289</v>
       </c>
       <c r="I194">
-        <v>3087154159</v>
+        <v>2478259986</v>
       </c>
     </row>
     <row r="195">
@@ -7550,7 +7550,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -7560,23 +7560,23 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Chưa có nhân viên thực hiện</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E195">
-        <v>16</v>
+        <v>111</v>
       </c>
       <c r="F195">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G195">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H195">
-        <v>16</v>
+        <v>111</v>
       </c>
       <c r="I195">
-        <v>122129629</v>
+        <v>846229904</v>
       </c>
     </row>
     <row r="196">
@@ -7587,33 +7587,33 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E196">
-        <v>319</v>
+        <v>82</v>
       </c>
       <c r="F196">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G196">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H196">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="I196">
-        <v>2068080513</v>
+        <v>670042361</v>
       </c>
     </row>
     <row r="197">
@@ -7624,33 +7624,33 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Chờ ký PLHĐ</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E197">
-        <v>24</v>
+        <v>416</v>
       </c>
       <c r="F197">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="G197">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="H197">
-        <v>24</v>
+        <v>416</v>
       </c>
       <c r="I197">
-        <v>178703703</v>
+        <v>3463921108</v>
       </c>
     </row>
     <row r="198">
@@ -7671,23 +7671,23 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Chưa có nhân viên thực hiện</t>
         </is>
       </c>
       <c r="E198">
-        <v>981</v>
+        <v>16</v>
       </c>
       <c r="F198">
-        <v>53</v>
+        <v>1</v>
       </c>
       <c r="G198">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="H198">
-        <v>862</v>
+        <v>16</v>
       </c>
       <c r="I198">
-        <v>7802347805</v>
+        <v>122129629</v>
       </c>
     </row>
     <row r="199">
@@ -7708,23 +7708,23 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E199">
-        <v>69</v>
+        <v>303</v>
       </c>
       <c r="F199">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G199">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H199">
-        <v>69</v>
+        <v>126</v>
       </c>
       <c r="I199">
-        <v>579094884</v>
+        <v>1942082513</v>
       </c>
     </row>
     <row r="200">
@@ -7740,28 +7740,28 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Chờ ký PLHĐ</t>
         </is>
       </c>
       <c r="E200">
-        <v>12</v>
+        <v>68</v>
       </c>
       <c r="F200">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G200">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H200">
-        <v>12</v>
+        <v>68</v>
       </c>
       <c r="I200">
-        <v>101407000</v>
+        <v>547202141</v>
       </c>
     </row>
     <row r="201">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -7782,23 +7782,23 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Chờ ký PLHĐ</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E201">
-        <v>2</v>
+        <v>901</v>
       </c>
       <c r="F201">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="G201">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="H201">
-        <v>2</v>
+        <v>798</v>
       </c>
       <c r="I201">
-        <v>11833333</v>
+        <v>7118480972</v>
       </c>
     </row>
     <row r="202">
@@ -7809,7 +7809,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -7819,23 +7819,23 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E202">
-        <v>255</v>
+        <v>85</v>
       </c>
       <c r="F202">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G202">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H202">
-        <v>245</v>
+        <v>85</v>
       </c>
       <c r="I202">
-        <v>1920228697</v>
+        <v>746092884</v>
       </c>
     </row>
     <row r="203">
@@ -7846,21 +7846,21 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E203">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F203">
         <v>1</v>
@@ -7869,10 +7869,10 @@
         <v>1</v>
       </c>
       <c r="H203">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I203">
-        <v>96357716</v>
+        <v>101407000</v>
       </c>
     </row>
     <row r="204">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>SLA</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -7897,19 +7897,19 @@
         </is>
       </c>
       <c r="E204">
-        <v>146</v>
+        <v>20</v>
       </c>
       <c r="F204">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G204">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H204">
-        <v>146</v>
+        <v>20</v>
       </c>
       <c r="I204">
-        <v>630587962</v>
+        <v>275925925</v>
       </c>
     </row>
     <row r="205">
@@ -7920,7 +7920,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>SLA</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -7930,23 +7930,23 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Chờ ký PLHĐ</t>
         </is>
       </c>
       <c r="E205">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="F205">
+        <v>1</v>
+      </c>
+      <c r="G205">
+        <v>1</v>
+      </c>
+      <c r="H205">
         <v>2</v>
       </c>
-      <c r="G205">
-        <v>2</v>
-      </c>
-      <c r="H205">
-        <v>32</v>
-      </c>
       <c r="I205">
-        <v>263271023</v>
+        <v>11833333</v>
       </c>
     </row>
     <row r="206">
@@ -7957,7 +7957,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -7967,23 +7967,23 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Chưa có nhân viên thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E206">
-        <v>10</v>
+        <v>261</v>
       </c>
       <c r="F206">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="G206">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="H206">
-        <v>10</v>
+        <v>251</v>
       </c>
       <c r="I206">
-        <v>104629629</v>
+        <v>1902426845</v>
       </c>
     </row>
     <row r="207">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -8004,23 +8004,23 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E207">
-        <v>177</v>
+        <v>10</v>
       </c>
       <c r="F207">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G207">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H207">
-        <v>149</v>
+        <v>10</v>
       </c>
       <c r="I207">
-        <v>1122443693</v>
+        <v>96357716</v>
       </c>
     </row>
     <row r="208">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>SLA</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -8041,23 +8041,23 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E208">
-        <v>355</v>
+        <v>146</v>
       </c>
       <c r="F208">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="G208">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H208">
-        <v>203</v>
+        <v>146</v>
       </c>
       <c r="I208">
-        <v>2315791127</v>
+        <v>630587962</v>
       </c>
     </row>
     <row r="209">
@@ -8068,7 +8068,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>SLA</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -8078,23 +8078,23 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E209">
-        <v>282</v>
+        <v>32</v>
       </c>
       <c r="F209">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="G209">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="H209">
-        <v>282</v>
+        <v>32</v>
       </c>
       <c r="I209">
-        <v>1845951677</v>
+        <v>263271023</v>
       </c>
     </row>
     <row r="210">
@@ -8110,28 +8110,28 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Chưa có nhân viên thực hiện</t>
         </is>
       </c>
       <c r="E210">
-        <v>159</v>
+        <v>10</v>
       </c>
       <c r="F210">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G210">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H210">
-        <v>159</v>
+        <v>10</v>
       </c>
       <c r="I210">
-        <v>1067110164</v>
+        <v>104629629</v>
       </c>
     </row>
     <row r="211">
@@ -8147,28 +8147,28 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Chờ ký PLHĐ</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E211">
-        <v>32</v>
+        <v>177</v>
       </c>
       <c r="F211">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G211">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H211">
-        <v>32</v>
+        <v>149</v>
       </c>
       <c r="I211">
-        <v>293518518</v>
+        <v>1122443693</v>
       </c>
     </row>
     <row r="212">
@@ -8184,7 +8184,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -8193,19 +8193,19 @@
         </is>
       </c>
       <c r="E212">
-        <v>119</v>
+        <v>314</v>
       </c>
       <c r="F212">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G212">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H212">
-        <v>119</v>
+        <v>162</v>
       </c>
       <c r="I212">
-        <v>903951849</v>
+        <v>2020292980</v>
       </c>
     </row>
     <row r="213">
@@ -8221,7 +8221,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -8230,19 +8230,19 @@
         </is>
       </c>
       <c r="E213">
-        <v>1365</v>
+        <v>350</v>
       </c>
       <c r="F213">
-        <v>72</v>
+        <v>18</v>
       </c>
       <c r="G213">
-        <v>72</v>
+        <v>18</v>
       </c>
       <c r="H213">
-        <v>1365</v>
+        <v>350</v>
       </c>
       <c r="I213">
-        <v>10254571540</v>
+        <v>2379412786</v>
       </c>
     </row>
     <row r="214">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -8267,19 +8267,19 @@
         </is>
       </c>
       <c r="E214">
-        <v>90</v>
+        <v>159</v>
       </c>
       <c r="F214">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G214">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H214">
-        <v>90</v>
+        <v>159</v>
       </c>
       <c r="I214">
-        <v>599253702</v>
+        <v>1067110164</v>
       </c>
     </row>
     <row r="215">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -8304,19 +8304,19 @@
         </is>
       </c>
       <c r="E215">
-        <v>110</v>
+        <v>32</v>
       </c>
       <c r="F215">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G215">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H215">
-        <v>110</v>
+        <v>32</v>
       </c>
       <c r="I215">
-        <v>867774792</v>
+        <v>293518518</v>
       </c>
     </row>
     <row r="216">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -8341,19 +8341,19 @@
         </is>
       </c>
       <c r="E216">
-        <v>698</v>
+        <v>119</v>
       </c>
       <c r="F216">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="G216">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="H216">
-        <v>614</v>
+        <v>119</v>
       </c>
       <c r="I216">
-        <v>5167398471</v>
+        <v>903951849</v>
       </c>
     </row>
     <row r="217">
@@ -8364,33 +8364,33 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E217">
-        <v>28</v>
+        <v>1341</v>
       </c>
       <c r="F217">
-        <v>1</v>
+        <v>71</v>
       </c>
       <c r="G217">
-        <v>1</v>
+        <v>71</v>
       </c>
       <c r="H217">
-        <v>28</v>
+        <v>1341</v>
       </c>
       <c r="I217">
-        <v>145441770</v>
+        <v>10089756726</v>
       </c>
     </row>
     <row r="218">
@@ -8401,7 +8401,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -8415,19 +8415,19 @@
         </is>
       </c>
       <c r="E218">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="F218">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G218">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H218">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="I218">
-        <v>692774069</v>
+        <v>599253702</v>
       </c>
     </row>
     <row r="219">
@@ -8438,7 +8438,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -8452,19 +8452,19 @@
         </is>
       </c>
       <c r="E219">
-        <v>32</v>
+        <v>110</v>
       </c>
       <c r="F219">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G219">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H219">
-        <v>32</v>
+        <v>110</v>
       </c>
       <c r="I219">
-        <v>268981481</v>
+        <v>867774792</v>
       </c>
     </row>
     <row r="220">
@@ -8475,7 +8475,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -8489,19 +8489,19 @@
         </is>
       </c>
       <c r="E220">
-        <v>511</v>
+        <v>688</v>
       </c>
       <c r="F220">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="G220">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="H220">
-        <v>499</v>
+        <v>604</v>
       </c>
       <c r="I220">
-        <v>4479271761</v>
+        <v>5068046620</v>
       </c>
     </row>
     <row r="221">
@@ -8512,7 +8512,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -8522,71 +8522,71 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E221">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F221">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G221">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H221">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I221">
-        <v>292129628</v>
+        <v>145441770</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Jinko 570</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E222">
-        <v>8</v>
+        <v>106</v>
       </c>
       <c r="F222">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G222">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H222">
-        <v>8</v>
+        <v>106</v>
       </c>
       <c r="I222">
-        <v>92961927</v>
+        <v>933998142</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -8596,71 +8596,71 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Chờ ký PLHĐ</t>
         </is>
       </c>
       <c r="E223">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="F223">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G223">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H223">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="I223">
-        <v>9090909</v>
+        <v>487463887</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E224">
-        <v>6</v>
+        <v>455</v>
       </c>
       <c r="F224">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="G224">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="H224">
-        <v>1</v>
+        <v>443</v>
       </c>
       <c r="I224">
-        <v>30314148</v>
+        <v>4019565282</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -8670,60 +8670,60 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E225">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F225">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G225">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H225">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I225">
-        <v>127671503</v>
+        <v>292129628</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>Jinko 570</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E226">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F226">
         <v>1</v>
       </c>
       <c r="G226">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H226">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I226">
-        <v>6181818</v>
+        <v>92961927</v>
       </c>
     </row>
     <row r="227">
@@ -8734,7 +8734,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -8744,11 +8744,11 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Chờ ký PLHĐ</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E227">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F227">
         <v>1</v>
@@ -8760,18 +8760,18 @@
         <v>0</v>
       </c>
       <c r="I227">
-        <v>10185185</v>
+        <v>9090909</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Longi 585</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -8785,10 +8785,10 @@
         </is>
       </c>
       <c r="E228">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F228">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G228">
         <v>0</v>
@@ -8797,18 +8797,18 @@
         <v>0</v>
       </c>
       <c r="I228">
-        <v>11180000</v>
+        <v>12870369</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -8818,11 +8818,11 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Chờ hàng TTQH</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E229">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="F229">
         <v>1</v>
@@ -8834,55 +8834,55 @@
         <v>0</v>
       </c>
       <c r="I229">
-        <v>1818181</v>
+        <v>127671503</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E230">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="F230">
         <v>1</v>
       </c>
       <c r="G230">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H230">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I230">
-        <v>154638888</v>
+        <v>6181818</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -8892,11 +8892,11 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Chờ ký PLHĐ</t>
         </is>
       </c>
       <c r="E231">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F231">
         <v>1</v>
@@ -8908,32 +8908,32 @@
         <v>0</v>
       </c>
       <c r="I231">
-        <v>9090909</v>
+        <v>10185185</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Chờ hàng CNCT</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E232">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F232">
         <v>1</v>
@@ -8945,7 +8945,7 @@
         <v>0</v>
       </c>
       <c r="I232">
-        <v>3636363</v>
+        <v>11180000</v>
       </c>
     </row>
     <row r="233">
@@ -8956,7 +8956,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -8966,23 +8966,23 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Chờ hàng TTQH</t>
         </is>
       </c>
       <c r="E233">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="F233">
         <v>1</v>
       </c>
       <c r="G233">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H233">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I233">
-        <v>72296140</v>
+        <v>1818181</v>
       </c>
     </row>
     <row r="234">
@@ -8993,21 +8993,21 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E234">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F234">
         <v>1</v>
@@ -9016,10 +9016,10 @@
         <v>1</v>
       </c>
       <c r="H234">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I234">
-        <v>116012600</v>
+        <v>154638888</v>
       </c>
     </row>
     <row r="235">
@@ -9030,7 +9030,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -9040,23 +9040,23 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E235">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F235">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G235">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H235">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I235">
-        <v>102287036</v>
+        <v>12727272</v>
       </c>
     </row>
     <row r="236">
@@ -9067,7 +9067,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -9077,11 +9077,11 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E236">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F236">
         <v>1</v>
@@ -9090,21 +9090,21 @@
         <v>1</v>
       </c>
       <c r="H236">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="I236">
-        <v>129629629</v>
+        <v>72296140</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -9114,34 +9114,34 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E237">
-        <v>127</v>
+        <v>12</v>
       </c>
       <c r="F237">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G237">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H237">
-        <v>127</v>
+        <v>12</v>
       </c>
       <c r="I237">
-        <v>1147559256</v>
+        <v>116012600</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -9151,34 +9151,34 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Chờ ký PLHĐ</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E238">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="F238">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G238">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H238">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="I238">
-        <v>522212961</v>
+        <v>102287036</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -9192,19 +9192,19 @@
         </is>
       </c>
       <c r="E239">
-        <v>850</v>
+        <v>24</v>
       </c>
       <c r="F239">
-        <v>67</v>
+        <v>1</v>
       </c>
       <c r="G239">
-        <v>63</v>
+        <v>1</v>
       </c>
       <c r="H239">
-        <v>777</v>
+        <v>24</v>
       </c>
       <c r="I239">
-        <v>7327397309</v>
+        <v>129629629</v>
       </c>
     </row>
     <row r="240">
@@ -9225,23 +9225,23 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E240">
-        <v>40</v>
+        <v>124</v>
       </c>
       <c r="F240">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G240">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H240">
-        <v>40</v>
+        <v>124</v>
       </c>
       <c r="I240">
-        <v>288425925</v>
+        <v>1160648144</v>
       </c>
     </row>
     <row r="241">
@@ -9257,28 +9257,28 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Chờ ký PLHĐ</t>
         </is>
       </c>
       <c r="E241">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F241">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G241">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H241">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="I241">
-        <v>65740740</v>
+        <v>287037036</v>
       </c>
     </row>
     <row r="242">
@@ -9294,28 +9294,28 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E242">
-        <v>38</v>
+        <v>882</v>
       </c>
       <c r="F242">
-        <v>4</v>
+        <v>71</v>
       </c>
       <c r="G242">
-        <v>4</v>
+        <v>65</v>
       </c>
       <c r="H242">
-        <v>38</v>
+        <v>786</v>
       </c>
       <c r="I242">
-        <v>312340740</v>
+        <v>7742727449</v>
       </c>
     </row>
     <row r="243">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -9336,23 +9336,23 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E243">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="F243">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G243">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H243">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="I243">
-        <v>315256480</v>
+        <v>344225925</v>
       </c>
     </row>
     <row r="244">
@@ -9363,33 +9363,33 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E244">
-        <v>206</v>
+        <v>35</v>
       </c>
       <c r="F244">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G244">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="H244">
-        <v>190</v>
+        <v>35</v>
       </c>
       <c r="I244">
-        <v>1600286567</v>
+        <v>328081481</v>
       </c>
     </row>
     <row r="245">
@@ -9400,7 +9400,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>CBG</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -9410,23 +9410,23 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E245">
-        <v>90</v>
+        <v>48</v>
       </c>
       <c r="F245">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G245">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H245">
-        <v>90</v>
+        <v>48</v>
       </c>
       <c r="I245">
-        <v>750863526</v>
+        <v>452983331</v>
       </c>
     </row>
     <row r="246">
@@ -9437,7 +9437,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -9447,23 +9447,23 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E246">
-        <v>76</v>
+        <v>222</v>
       </c>
       <c r="F246">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="G246">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="H246">
-        <v>76</v>
+        <v>204</v>
       </c>
       <c r="I246">
-        <v>394551604</v>
+        <v>1726037493</v>
       </c>
     </row>
     <row r="247">
@@ -9474,7 +9474,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>CBG</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -9488,7 +9488,7 @@
         </is>
       </c>
       <c r="E247">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F247">
         <v>1</v>
@@ -9497,10 +9497,10 @@
         <v>1</v>
       </c>
       <c r="H247">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I247">
-        <v>83333333</v>
+        <v>113556731</v>
       </c>
     </row>
     <row r="248">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>CBG</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -9525,19 +9525,19 @@
         </is>
       </c>
       <c r="E248">
-        <v>187</v>
+        <v>76</v>
       </c>
       <c r="F248">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="G248">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H248">
-        <v>131</v>
+        <v>76</v>
       </c>
       <c r="I248">
-        <v>1626231445</v>
+        <v>637306795</v>
       </c>
     </row>
     <row r="249">
@@ -9558,23 +9558,23 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E249">
-        <v>9</v>
+        <v>76</v>
       </c>
       <c r="F249">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G249">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H249">
-        <v>9</v>
+        <v>76</v>
       </c>
       <c r="I249">
-        <v>92592592</v>
+        <v>394551604</v>
       </c>
     </row>
     <row r="250">
@@ -9590,16 +9590,16 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Chờ ký PLHĐ</t>
         </is>
       </c>
       <c r="E250">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F250">
         <v>1</v>
@@ -9608,10 +9608,10 @@
         <v>1</v>
       </c>
       <c r="H250">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I250">
-        <v>29019444</v>
+        <v>83333333</v>
       </c>
     </row>
     <row r="251">
@@ -9622,7 +9622,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -9632,23 +9632,23 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E251">
-        <v>119</v>
+        <v>187</v>
       </c>
       <c r="F251">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G251">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H251">
-        <v>119</v>
+        <v>155</v>
       </c>
       <c r="I251">
-        <v>1028680737</v>
+        <v>1626231445</v>
       </c>
     </row>
     <row r="252">
@@ -9659,7 +9659,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -9669,7 +9669,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Chờ ký PLHĐ</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E252">
@@ -9685,7 +9685,7 @@
         <v>9</v>
       </c>
       <c r="I252">
-        <v>102346759</v>
+        <v>92592592</v>
       </c>
     </row>
     <row r="253">
@@ -9706,23 +9706,23 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E253">
-        <v>955</v>
+        <v>114</v>
       </c>
       <c r="F253">
-        <v>66</v>
+        <v>11</v>
       </c>
       <c r="G253">
-        <v>58</v>
+        <v>11</v>
       </c>
       <c r="H253">
-        <v>814</v>
+        <v>114</v>
       </c>
       <c r="I253">
-        <v>8578704937</v>
+        <v>1008090182</v>
       </c>
     </row>
     <row r="254">
@@ -9743,11 +9743,11 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Chờ ký PLHĐ</t>
         </is>
       </c>
       <c r="E254">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="F254">
         <v>3</v>
@@ -9756,10 +9756,10 @@
         <v>3</v>
       </c>
       <c r="H254">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="I254">
-        <v>400329258</v>
+        <v>306583795</v>
       </c>
     </row>
     <row r="255">
@@ -9770,7 +9770,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>DBN</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -9784,19 +9784,19 @@
         </is>
       </c>
       <c r="E255">
-        <v>40</v>
+        <v>898</v>
       </c>
       <c r="F255">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="G255">
-        <v>2</v>
+        <v>57</v>
       </c>
       <c r="H255">
-        <v>40</v>
+        <v>776</v>
       </c>
       <c r="I255">
-        <v>292314814</v>
+        <v>8089566370</v>
       </c>
     </row>
     <row r="256">
@@ -9807,7 +9807,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -9817,23 +9817,23 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E256">
-        <v>28</v>
+        <v>97</v>
       </c>
       <c r="F256">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G256">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H256">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="I256">
-        <v>147222222</v>
+        <v>823413936</v>
       </c>
     </row>
     <row r="257">
@@ -9844,7 +9844,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>DBN</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -9854,11 +9854,11 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Chờ ký PLHĐ</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E257">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="F257">
         <v>2</v>
@@ -9867,10 +9867,10 @@
         <v>2</v>
       </c>
       <c r="H257">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="I257">
-        <v>185708532</v>
+        <v>292314814</v>
       </c>
     </row>
     <row r="258">
@@ -9891,23 +9891,23 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E258">
-        <v>199</v>
+        <v>28</v>
       </c>
       <c r="F258">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G258">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H258">
-        <v>199</v>
+        <v>0</v>
       </c>
       <c r="I258">
-        <v>1298170364</v>
+        <v>147222222</v>
       </c>
     </row>
     <row r="259">
@@ -9928,11 +9928,11 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Chờ ký PLHĐ</t>
         </is>
       </c>
       <c r="E259">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="F259">
         <v>1</v>
@@ -9941,10 +9941,10 @@
         <v>1</v>
       </c>
       <c r="H259">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="I259">
-        <v>98148148</v>
+        <v>81171495</v>
       </c>
     </row>
     <row r="260">
@@ -9960,28 +9960,28 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E260">
-        <v>1</v>
+        <v>199</v>
       </c>
       <c r="F260">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G260">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H260">
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="I260">
-        <v>2592592</v>
+        <v>1298170364</v>
       </c>
     </row>
     <row r="261">
@@ -9992,7 +9992,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -10002,23 +10002,23 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E261">
-        <v>74</v>
+        <v>24</v>
       </c>
       <c r="F261">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G261">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H261">
-        <v>74</v>
+        <v>24</v>
       </c>
       <c r="I261">
-        <v>549999999</v>
+        <v>98148148</v>
       </c>
     </row>
     <row r="262">
@@ -10029,33 +10029,33 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Chờ ký PLHĐ</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E262">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F262">
         <v>1</v>
       </c>
       <c r="G262">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H262">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I262">
-        <v>66666666</v>
+        <v>2592592</v>
       </c>
     </row>
     <row r="263">
@@ -10076,23 +10076,23 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E263">
-        <v>149</v>
+        <v>74</v>
       </c>
       <c r="F263">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G263">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H263">
-        <v>133</v>
+        <v>74</v>
       </c>
       <c r="I263">
-        <v>1045544440</v>
+        <v>549999999</v>
       </c>
     </row>
     <row r="264">
@@ -10113,23 +10113,23 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E264">
-        <v>28</v>
+        <v>149</v>
       </c>
       <c r="F264">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G264">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H264">
-        <v>28</v>
+        <v>149</v>
       </c>
       <c r="I264">
-        <v>201317592</v>
+        <v>1045544440</v>
       </c>
     </row>
     <row r="265">
@@ -10145,7 +10145,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -10154,19 +10154,19 @@
         </is>
       </c>
       <c r="E265">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="F265">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G265">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H265">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="I265">
-        <v>119148148</v>
+        <v>267984258</v>
       </c>
     </row>
     <row r="266">
@@ -10177,33 +10177,33 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E266">
-        <v>306</v>
+        <v>14</v>
       </c>
       <c r="F266">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="G266">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H266">
-        <v>167</v>
+        <v>14</v>
       </c>
       <c r="I266">
-        <v>2545874266</v>
+        <v>119148148</v>
       </c>
     </row>
     <row r="267">
@@ -10214,7 +10214,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -10224,23 +10224,23 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Chưa có nhân viên thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E267">
-        <v>34</v>
+        <v>346</v>
       </c>
       <c r="F267">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="G267">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="H267">
-        <v>34</v>
+        <v>259</v>
       </c>
       <c r="I267">
-        <v>305590802</v>
+        <v>2803838831</v>
       </c>
     </row>
     <row r="268">
@@ -10261,23 +10261,23 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Chưa có nhân viên thực hiện</t>
         </is>
       </c>
       <c r="E268">
-        <v>94</v>
+        <v>34</v>
       </c>
       <c r="F268">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G268">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H268">
-        <v>94</v>
+        <v>34</v>
       </c>
       <c r="I268">
-        <v>915018516</v>
+        <v>305590802</v>
       </c>
     </row>
     <row r="269">
@@ -10298,23 +10298,23 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E269">
-        <v>1211</v>
+        <v>208</v>
       </c>
       <c r="F269">
-        <v>89</v>
+        <v>17</v>
       </c>
       <c r="G269">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="H269">
-        <v>1000</v>
+        <v>178</v>
       </c>
       <c r="I269">
-        <v>10382389922</v>
+        <v>1878237157</v>
       </c>
     </row>
     <row r="270">
@@ -10335,23 +10335,23 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E270">
-        <v>375</v>
+        <v>1101</v>
       </c>
       <c r="F270">
-        <v>32</v>
+        <v>78</v>
       </c>
       <c r="G270">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="H270">
-        <v>375</v>
+        <v>905</v>
       </c>
       <c r="I270">
-        <v>3211853505</v>
+        <v>9306868895</v>
       </c>
     </row>
     <row r="271">
@@ -10367,7 +10367,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -10376,19 +10376,19 @@
         </is>
       </c>
       <c r="E271">
-        <v>42</v>
+        <v>487</v>
       </c>
       <c r="F271">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="G271">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="H271">
-        <v>42</v>
+        <v>487</v>
       </c>
       <c r="I271">
-        <v>384629628</v>
+        <v>4303683665</v>
       </c>
     </row>
     <row r="272">
@@ -10399,33 +10399,33 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E272">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="F272">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G272">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H272">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="I272">
-        <v>34470000</v>
+        <v>384629628</v>
       </c>
     </row>
     <row r="273">
@@ -10446,23 +10446,23 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E273">
-        <v>120</v>
+        <v>10</v>
       </c>
       <c r="F273">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G273">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H273">
-        <v>120</v>
+        <v>10</v>
       </c>
       <c r="I273">
-        <v>861955756</v>
+        <v>34470000</v>
       </c>
     </row>
     <row r="274">
@@ -10473,7 +10473,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -10483,23 +10483,23 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E274">
-        <v>54</v>
+        <v>120</v>
       </c>
       <c r="F274">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G274">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H274">
-        <v>54</v>
+        <v>120</v>
       </c>
       <c r="I274">
-        <v>403854443</v>
+        <v>861955756</v>
       </c>
     </row>
     <row r="275">
@@ -10520,23 +10520,23 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>Chờ ký PLHĐ</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E275">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="F275">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G275">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H275">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="I275">
-        <v>222222222</v>
+        <v>403854443</v>
       </c>
     </row>
     <row r="276">
@@ -10557,23 +10557,23 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Chờ ký PLHĐ</t>
         </is>
       </c>
       <c r="E276">
-        <v>342</v>
+        <v>30</v>
       </c>
       <c r="F276">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="G276">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="H276">
-        <v>263</v>
+        <v>30</v>
       </c>
       <c r="I276">
-        <v>2682069096</v>
+        <v>222222222</v>
       </c>
     </row>
     <row r="277">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -10594,23 +10594,23 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E277">
-        <v>58</v>
+        <v>372</v>
       </c>
       <c r="F277">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="G277">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="H277">
-        <v>58</v>
+        <v>295</v>
       </c>
       <c r="I277">
-        <v>455546888</v>
+        <v>2972954683</v>
       </c>
     </row>
     <row r="278">
@@ -10631,11 +10631,11 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Chờ ký PLHĐ</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E278">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F278">
         <v>4</v>
@@ -10644,10 +10644,10 @@
         <v>4</v>
       </c>
       <c r="H278">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I278">
-        <v>421079000</v>
+        <v>455546888</v>
       </c>
     </row>
     <row r="279">
@@ -10668,23 +10668,23 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Chờ ký PLHĐ</t>
         </is>
       </c>
       <c r="E279">
-        <v>1311</v>
+        <v>67</v>
       </c>
       <c r="F279">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="G279">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="H279">
-        <v>895</v>
+        <v>67</v>
       </c>
       <c r="I279">
-        <v>8679596368</v>
+        <v>464271771</v>
       </c>
     </row>
     <row r="280">
@@ -10705,23 +10705,23 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E280">
-        <v>42</v>
+        <v>1299</v>
       </c>
       <c r="F280">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="G280">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="H280">
-        <v>42</v>
+        <v>930</v>
       </c>
       <c r="I280">
-        <v>347404240</v>
+        <v>8625637697</v>
       </c>
     </row>
     <row r="281">
@@ -10737,28 +10737,28 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Chờ ký PLHĐ</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E281">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="F281">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G281">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H281">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="I281">
-        <v>88291079</v>
+        <v>237442587</v>
       </c>
     </row>
     <row r="282">
@@ -10779,23 +10779,23 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Chờ ký PLHĐ</t>
         </is>
       </c>
       <c r="E282">
-        <v>85</v>
+        <v>12</v>
       </c>
       <c r="F282">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G282">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H282">
-        <v>85</v>
+        <v>12</v>
       </c>
       <c r="I282">
-        <v>634498481</v>
+        <v>88291079</v>
       </c>
     </row>
     <row r="283">
@@ -10816,23 +10816,23 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E283">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="F283">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G283">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H283">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="I283">
-        <v>170259259</v>
+        <v>634498481</v>
       </c>
     </row>
     <row r="284">
@@ -10843,33 +10843,33 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E284">
-        <v>534</v>
+        <v>20</v>
       </c>
       <c r="F284">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="G284">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="H284">
-        <v>534</v>
+        <v>20</v>
       </c>
       <c r="I284">
-        <v>4421102064</v>
+        <v>170259259</v>
       </c>
     </row>
     <row r="285">
@@ -10885,16 +10885,16 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E285">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F285">
         <v>1</v>
@@ -10903,10 +10903,10 @@
         <v>1</v>
       </c>
       <c r="H285">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="I285">
-        <v>128981481</v>
+        <v>237037037</v>
       </c>
     </row>
     <row r="286">
@@ -10917,7 +10917,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -10931,19 +10931,19 @@
         </is>
       </c>
       <c r="E286">
-        <v>97</v>
+        <v>472</v>
       </c>
       <c r="F286">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="G286">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="H286">
-        <v>97</v>
+        <v>472</v>
       </c>
       <c r="I286">
-        <v>865192589</v>
+        <v>4012213176</v>
       </c>
     </row>
     <row r="287">
@@ -10954,7 +10954,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -10964,23 +10964,23 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E287">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="F287">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G287">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H287">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="I287">
-        <v>292102777</v>
+        <v>171851851</v>
       </c>
     </row>
     <row r="288">
@@ -10991,12 +10991,12 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -11005,19 +11005,19 @@
         </is>
       </c>
       <c r="E288">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F288">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G288">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H288">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="I288">
-        <v>258261388</v>
+        <v>128981481</v>
       </c>
     </row>
     <row r="289">
@@ -11028,7 +11028,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -11042,19 +11042,19 @@
         </is>
       </c>
       <c r="E289">
-        <v>806</v>
+        <v>97</v>
       </c>
       <c r="F289">
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="G289">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="H289">
-        <v>734</v>
+        <v>97</v>
       </c>
       <c r="I289">
-        <v>5780650625</v>
+        <v>865192589</v>
       </c>
     </row>
     <row r="290">
@@ -11075,23 +11075,23 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E290">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="F290">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G290">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H290">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="I290">
-        <v>516335091</v>
+        <v>292102777</v>
       </c>
     </row>
     <row r="291">
@@ -11102,7 +11102,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -11112,23 +11112,23 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Chờ ký PLHĐ</t>
         </is>
       </c>
       <c r="E291">
-        <v>164</v>
+        <v>34</v>
       </c>
       <c r="F291">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G291">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H291">
-        <v>164</v>
+        <v>34</v>
       </c>
       <c r="I291">
-        <v>1351913395</v>
+        <v>258261388</v>
       </c>
     </row>
     <row r="292">
@@ -11139,7 +11139,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>LCU</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -11153,19 +11153,19 @@
         </is>
       </c>
       <c r="E292">
-        <v>18</v>
+        <v>803</v>
       </c>
       <c r="F292">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="G292">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="H292">
-        <v>18</v>
+        <v>779</v>
       </c>
       <c r="I292">
-        <v>159200000</v>
+        <v>5858533958</v>
       </c>
     </row>
     <row r="293">
@@ -11176,7 +11176,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -11186,23 +11186,23 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E293">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="F293">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G293">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H293">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="I293">
-        <v>79788148</v>
+        <v>516335091</v>
       </c>
     </row>
     <row r="294">
@@ -11213,7 +11213,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -11227,19 +11227,19 @@
         </is>
       </c>
       <c r="E294">
-        <v>40</v>
+        <v>164</v>
       </c>
       <c r="F294">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G294">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H294">
-        <v>30</v>
+        <v>164</v>
       </c>
       <c r="I294">
-        <v>284166666</v>
+        <v>1351913395</v>
       </c>
     </row>
     <row r="295">
@@ -11250,7 +11250,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>LCU</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -11264,19 +11264,19 @@
         </is>
       </c>
       <c r="E295">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="F295">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G295">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H295">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="I295">
-        <v>322685184</v>
+        <v>159200000</v>
       </c>
     </row>
     <row r="296">
@@ -11287,7 +11287,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -11301,7 +11301,7 @@
         </is>
       </c>
       <c r="E296">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F296">
         <v>1</v>
@@ -11310,10 +11310,10 @@
         <v>1</v>
       </c>
       <c r="H296">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I296">
-        <v>167000000</v>
+        <v>79788148</v>
       </c>
     </row>
     <row r="297">
@@ -11324,7 +11324,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -11334,23 +11334,23 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Chờ ký PLHĐ</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E297">
-        <v>26</v>
+        <v>78</v>
       </c>
       <c r="F297">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G297">
         <v>2</v>
       </c>
       <c r="H297">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I297">
-        <v>244922663</v>
+        <v>672661109</v>
       </c>
     </row>
     <row r="298">
@@ -11361,7 +11361,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -11375,19 +11375,19 @@
         </is>
       </c>
       <c r="E298">
-        <v>737</v>
+        <v>36</v>
       </c>
       <c r="F298">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="G298">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="H298">
-        <v>703</v>
+        <v>36</v>
       </c>
       <c r="I298">
-        <v>6831488903</v>
+        <v>322685184</v>
       </c>
     </row>
     <row r="299">
@@ -11398,7 +11398,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -11412,19 +11412,19 @@
         </is>
       </c>
       <c r="E299">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="F299">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G299">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H299">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="I299">
-        <v>269687192</v>
+        <v>167000000</v>
       </c>
     </row>
     <row r="300">
@@ -11435,7 +11435,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -11449,19 +11449,19 @@
         </is>
       </c>
       <c r="E300">
-        <v>89</v>
+        <v>26</v>
       </c>
       <c r="F300">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G300">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H300">
-        <v>89</v>
+        <v>26</v>
       </c>
       <c r="I300">
-        <v>400289814</v>
+        <v>244922663</v>
       </c>
     </row>
     <row r="301">
@@ -11472,7 +11472,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -11486,19 +11486,19 @@
         </is>
       </c>
       <c r="E301">
-        <v>622</v>
+        <v>781</v>
       </c>
       <c r="F301">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="G301">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="H301">
-        <v>622</v>
+        <v>717</v>
       </c>
       <c r="I301">
-        <v>4048406234</v>
+        <v>7183417606</v>
       </c>
     </row>
     <row r="302">
@@ -11509,7 +11509,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -11535,7 +11535,7 @@
         <v>68</v>
       </c>
       <c r="I302">
-        <v>571799441</v>
+        <v>580526397</v>
       </c>
     </row>
     <row r="303">
@@ -11546,7 +11546,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -11560,19 +11560,19 @@
         </is>
       </c>
       <c r="E303">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="F303">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G303">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H303">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I303">
-        <v>153686708</v>
+        <v>400289814</v>
       </c>
     </row>
     <row r="304">
@@ -11583,7 +11583,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -11597,19 +11597,19 @@
         </is>
       </c>
       <c r="E304">
-        <v>714</v>
+        <v>602</v>
       </c>
       <c r="F304">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="G304">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="H304">
-        <v>628</v>
+        <v>602</v>
       </c>
       <c r="I304">
-        <v>6428794174</v>
+        <v>3823476186</v>
       </c>
     </row>
     <row r="305">
@@ -11630,11 +11630,11 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E305">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F305">
         <v>4</v>
@@ -11643,10 +11643,10 @@
         <v>4</v>
       </c>
       <c r="H305">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I305">
-        <v>516853479</v>
+        <v>571799441</v>
       </c>
     </row>
     <row r="306">
@@ -11662,7 +11662,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="E306">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F306">
         <v>1</v>
@@ -11680,10 +11680,10 @@
         <v>1</v>
       </c>
       <c r="H306">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I306">
-        <v>198981481</v>
+        <v>153686708</v>
       </c>
     </row>
     <row r="307">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -11708,19 +11708,19 @@
         </is>
       </c>
       <c r="E307">
-        <v>40</v>
+        <v>740</v>
       </c>
       <c r="F307">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="G307">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="H307">
-        <v>40</v>
+        <v>694</v>
       </c>
       <c r="I307">
-        <v>358333332</v>
+        <v>6577960840</v>
       </c>
     </row>
     <row r="308">
@@ -11736,7 +11736,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -11745,19 +11745,19 @@
         </is>
       </c>
       <c r="E308">
-        <v>552</v>
+        <v>70</v>
       </c>
       <c r="F308">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="G308">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="H308">
-        <v>552</v>
+        <v>70</v>
       </c>
       <c r="I308">
-        <v>4833516515</v>
+        <v>516853479</v>
       </c>
     </row>
     <row r="309">
@@ -11768,12 +11768,12 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -11782,7 +11782,7 @@
         </is>
       </c>
       <c r="E309">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F309">
         <v>1</v>
@@ -11791,10 +11791,10 @@
         <v>1</v>
       </c>
       <c r="H309">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I309">
-        <v>160818421</v>
+        <v>198981481</v>
       </c>
     </row>
     <row r="310">
@@ -11805,12 +11805,12 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -11819,19 +11819,19 @@
         </is>
       </c>
       <c r="E310">
-        <v>319</v>
+        <v>40</v>
       </c>
       <c r="F310">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="G310">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="H310">
-        <v>223</v>
+        <v>40</v>
       </c>
       <c r="I310">
-        <v>2843433601</v>
+        <v>358333332</v>
       </c>
     </row>
     <row r="311">
@@ -11842,33 +11842,33 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E311">
-        <v>62</v>
+        <v>552</v>
       </c>
       <c r="F311">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="G311">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="H311">
-        <v>62</v>
+        <v>552</v>
       </c>
       <c r="I311">
-        <v>581851850</v>
+        <v>4833516515</v>
       </c>
     </row>
     <row r="312">
@@ -11879,7 +11879,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -11893,19 +11893,19 @@
         </is>
       </c>
       <c r="E312">
-        <v>93</v>
+        <v>18</v>
       </c>
       <c r="F312">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G312">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H312">
-        <v>93</v>
+        <v>18</v>
       </c>
       <c r="I312">
-        <v>462962962</v>
+        <v>160818421</v>
       </c>
     </row>
     <row r="313">
@@ -11916,7 +11916,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -11930,19 +11930,19 @@
         </is>
       </c>
       <c r="E313">
-        <v>475</v>
+        <v>361</v>
       </c>
       <c r="F313">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G313">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="H313">
-        <v>310</v>
+        <v>257</v>
       </c>
       <c r="I313">
-        <v>2514473645</v>
+        <v>3262051052</v>
       </c>
     </row>
     <row r="314">
@@ -11953,7 +11953,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -11967,19 +11967,19 @@
         </is>
       </c>
       <c r="E314">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="F314">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G314">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H314">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="I314">
-        <v>231802262</v>
+        <v>581851850</v>
       </c>
     </row>
     <row r="315">
@@ -11990,7 +11990,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -12000,23 +12000,23 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Chờ ký PLHĐ</t>
         </is>
       </c>
       <c r="E315">
-        <v>236</v>
+        <v>93</v>
       </c>
       <c r="F315">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G315">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H315">
-        <v>236</v>
+        <v>93</v>
       </c>
       <c r="I315">
-        <v>1504051583</v>
+        <v>462962962</v>
       </c>
     </row>
     <row r="316">
@@ -12027,7 +12027,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -12037,23 +12037,23 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E316">
-        <v>56</v>
+        <v>502</v>
       </c>
       <c r="F316">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="G316">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H316">
-        <v>56</v>
+        <v>363</v>
       </c>
       <c r="I316">
-        <v>549915837</v>
+        <v>2684141645</v>
       </c>
     </row>
     <row r="317">
@@ -12069,28 +12069,28 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E317">
-        <v>16</v>
+        <v>147</v>
       </c>
       <c r="F317">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G317">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H317">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="I317">
-        <v>37037037</v>
+        <v>891441092</v>
       </c>
     </row>
     <row r="318">
@@ -12101,7 +12101,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>SLA</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -12111,23 +12111,23 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E318">
-        <v>120</v>
+        <v>169</v>
       </c>
       <c r="F318">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G318">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H318">
-        <v>120</v>
+        <v>169</v>
       </c>
       <c r="I318">
-        <v>913748272</v>
+        <v>1394328590</v>
       </c>
     </row>
     <row r="319">
@@ -12138,33 +12138,33 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E319">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="F319">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G319">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H319">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I319">
-        <v>235430554</v>
+        <v>37037037</v>
       </c>
     </row>
     <row r="320">
@@ -12175,7 +12175,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>SLA</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -12185,23 +12185,23 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Chờ ký PLHĐ</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E320">
-        <v>18</v>
+        <v>120</v>
       </c>
       <c r="F320">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G320">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H320">
-        <v>18</v>
+        <v>120</v>
       </c>
       <c r="I320">
-        <v>135641666</v>
+        <v>913748272</v>
       </c>
     </row>
     <row r="321">
@@ -12222,23 +12222,23 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E321">
-        <v>525</v>
+        <v>85</v>
       </c>
       <c r="F321">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="G321">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="H321">
-        <v>395</v>
+        <v>74</v>
       </c>
       <c r="I321">
-        <v>4088236807</v>
+        <v>575060182</v>
       </c>
     </row>
     <row r="322">
@@ -12259,23 +12259,23 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Chờ ký PLHĐ</t>
         </is>
       </c>
       <c r="E322">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="F322">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G322">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H322">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="I322">
-        <v>519438718</v>
+        <v>135641666</v>
       </c>
     </row>
     <row r="323">
@@ -12291,28 +12291,28 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E323">
-        <v>14</v>
+        <v>415</v>
       </c>
       <c r="F323">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="G323">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="H323">
-        <v>14</v>
+        <v>349</v>
       </c>
       <c r="I323">
-        <v>109259259</v>
+        <v>3220829403</v>
       </c>
     </row>
     <row r="324">
@@ -12328,28 +12328,28 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E324">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="F324">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G324">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H324">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="I324">
-        <v>404166666</v>
+        <v>940549827</v>
       </c>
     </row>
     <row r="325">
@@ -12370,23 +12370,23 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E325">
-        <v>130</v>
+        <v>14</v>
       </c>
       <c r="F325">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G325">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H325">
-        <v>130</v>
+        <v>14</v>
       </c>
       <c r="I325">
-        <v>1013370366</v>
+        <v>109259259</v>
       </c>
     </row>
     <row r="326">
@@ -12397,33 +12397,33 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E326">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="F326">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G326">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H326">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="I326">
-        <v>720925923</v>
+        <v>404166666</v>
       </c>
     </row>
     <row r="327">
@@ -12434,33 +12434,33 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>Chờ ký PLHĐ</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E327">
-        <v>44</v>
+        <v>142</v>
       </c>
       <c r="F327">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G327">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="H327">
-        <v>44</v>
+        <v>142</v>
       </c>
       <c r="I327">
-        <v>413075093</v>
+        <v>1120037033</v>
       </c>
     </row>
     <row r="328">
@@ -12481,23 +12481,23 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E328">
-        <v>418</v>
+        <v>76</v>
       </c>
       <c r="F328">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="G328">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="H328">
-        <v>406</v>
+        <v>76</v>
       </c>
       <c r="I328">
-        <v>3934148882</v>
+        <v>662962961</v>
       </c>
     </row>
     <row r="329">
@@ -12518,11 +12518,11 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Chờ ký PLHĐ</t>
         </is>
       </c>
       <c r="E329">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="F329">
         <v>3</v>
@@ -12531,10 +12531,10 @@
         <v>3</v>
       </c>
       <c r="H329">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="I329">
-        <v>312499998</v>
+        <v>413075093</v>
       </c>
     </row>
     <row r="330">
@@ -12550,28 +12550,28 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E330">
-        <v>173</v>
+        <v>446</v>
       </c>
       <c r="F330">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="G330">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="H330">
-        <v>173</v>
+        <v>418</v>
       </c>
       <c r="I330">
-        <v>1279148143</v>
+        <v>4072667399</v>
       </c>
     </row>
     <row r="331">
@@ -12582,7 +12582,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -12592,23 +12592,23 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E331">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F331">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G331">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H331">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="I331">
-        <v>174074074</v>
+        <v>312499998</v>
       </c>
     </row>
     <row r="332">
@@ -12619,33 +12619,33 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>Chờ ký PLHĐ</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E332">
-        <v>26</v>
+        <v>173</v>
       </c>
       <c r="F332">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G332">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H332">
-        <v>12</v>
+        <v>173</v>
       </c>
       <c r="I332">
-        <v>228703702</v>
+        <v>1279148143</v>
       </c>
     </row>
     <row r="333">
@@ -12666,23 +12666,23 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E333">
-        <v>356</v>
+        <v>42</v>
       </c>
       <c r="F333">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="G333">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="H333">
-        <v>356</v>
+        <v>42</v>
       </c>
       <c r="I333">
-        <v>2689117582</v>
+        <v>279738888</v>
       </c>
     </row>
     <row r="334">
@@ -12693,7 +12693,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -12703,23 +12703,23 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Chờ ký PLHĐ</t>
         </is>
       </c>
       <c r="E334">
-        <v>200</v>
+        <v>26</v>
       </c>
       <c r="F334">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="G334">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="H334">
-        <v>200</v>
+        <v>12</v>
       </c>
       <c r="I334">
-        <v>1630958834</v>
+        <v>228703702</v>
       </c>
     </row>
     <row r="335">
@@ -12730,7 +12730,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -12740,23 +12740,23 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>Chờ ký PLHĐ</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E335">
-        <v>14</v>
+        <v>356</v>
       </c>
       <c r="F335">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="G335">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="H335">
-        <v>14</v>
+        <v>356</v>
       </c>
       <c r="I335">
-        <v>116927407</v>
+        <v>2689117582</v>
       </c>
     </row>
     <row r="336">
@@ -12777,23 +12777,23 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E336">
-        <v>135</v>
+        <v>200</v>
       </c>
       <c r="F336">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G336">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H336">
-        <v>101</v>
+        <v>200</v>
       </c>
       <c r="I336">
-        <v>1096427773</v>
+        <v>1630958834</v>
       </c>
     </row>
     <row r="337">
@@ -12814,23 +12814,23 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Chờ ký PLHĐ</t>
         </is>
       </c>
       <c r="E337">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="F337">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G337">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H337">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="I337">
-        <v>520623610</v>
+        <v>165075555</v>
       </c>
     </row>
     <row r="338">
@@ -12846,28 +12846,28 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E338">
-        <v>30</v>
+        <v>130</v>
       </c>
       <c r="F338">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="G338">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H338">
-        <v>30</v>
+        <v>96</v>
       </c>
       <c r="I338">
-        <v>237712962</v>
+        <v>1048279625</v>
       </c>
     </row>
     <row r="339">
@@ -12883,7 +12883,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Đã map wms</t>
+          <t>Chưa map wms</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -12892,19 +12892,19 @@
         </is>
       </c>
       <c r="E339">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="F339">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G339">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H339">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="I339">
-        <v>212267592</v>
+        <v>520623610</v>
       </c>
     </row>
     <row r="340">
@@ -12915,12 +12915,12 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -12929,19 +12929,19 @@
         </is>
       </c>
       <c r="E340">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="F340">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G340">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H340">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="I340">
-        <v>446296294</v>
+        <v>237712962</v>
       </c>
     </row>
     <row r="341">
@@ -12952,33 +12952,33 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Chưa map wms</t>
+          <t>Đã map wms</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>Chờ ký PLHĐ</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E341">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="F341">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G341">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H341">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="I341">
-        <v>63888888</v>
+        <v>212267592</v>
       </c>
     </row>
     <row r="342">
@@ -12999,23 +12999,23 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E342">
-        <v>910</v>
+        <v>430</v>
       </c>
       <c r="F342">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="G342">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="H342">
-        <v>900</v>
+        <v>430</v>
       </c>
       <c r="I342">
-        <v>7679551576</v>
+        <v>3706351135</v>
       </c>
     </row>
     <row r="343">
@@ -13036,23 +13036,23 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Chờ ký PLHĐ</t>
         </is>
       </c>
       <c r="E343">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="F343">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G343">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H343">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="I343">
-        <v>145370370</v>
+        <v>63888888</v>
       </c>
     </row>
     <row r="344">
@@ -13063,7 +13063,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -13073,23 +13073,23 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E344">
-        <v>73</v>
+        <v>533</v>
       </c>
       <c r="F344">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="G344">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="H344">
-        <v>72</v>
+        <v>523</v>
       </c>
       <c r="I344">
-        <v>630712960</v>
+        <v>4425724216</v>
       </c>
     </row>
     <row r="345">
@@ -13100,7 +13100,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -13110,23 +13110,23 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>Chờ ký PLHĐ</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="E345">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="F345">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G345">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H345">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="I345">
-        <v>48072000</v>
+        <v>239460184</v>
       </c>
     </row>
     <row r="346">
@@ -13147,23 +13147,23 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="E346">
-        <v>275</v>
+        <v>62</v>
       </c>
       <c r="F346">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="G346">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="H346">
-        <v>225</v>
+        <v>62</v>
       </c>
       <c r="I346">
-        <v>2390180379</v>
+        <v>578305553</v>
       </c>
     </row>
     <row r="347">
@@ -13184,34 +13184,34 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Chờ ký PLHĐ</t>
         </is>
       </c>
       <c r="E347">
-        <v>147</v>
+        <v>10</v>
       </c>
       <c r="F347">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G347">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H347">
-        <v>115</v>
+        <v>10</v>
       </c>
       <c r="I347">
-        <v>1027702149</v>
+        <v>50000000</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -13221,60 +13221,171 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="E348">
-        <v>18</v>
+        <v>321</v>
       </c>
       <c r="F348">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="G348">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="H348">
-        <v>18</v>
+        <v>291</v>
       </c>
       <c r="I348">
-        <v>162072285</v>
+        <v>2768154423</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>VLG</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>Chưa map wms</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>Đang thực hiện</t>
+        </is>
+      </c>
+      <c r="E349">
+        <v>147</v>
+      </c>
+      <c r="F349">
+        <v>8</v>
+      </c>
+      <c r="G349">
+        <v>7</v>
+      </c>
+      <c r="H349">
+        <v>115</v>
+      </c>
+      <c r="I349">
+        <v>1027702149</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
           <t>TCT_Pin khác</t>
         </is>
       </c>
-      <c r="B349" t="inlineStr">
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>DTP</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>Chưa map wms</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>Đang thực hiện</t>
+        </is>
+      </c>
+      <c r="E350">
+        <v>18</v>
+      </c>
+      <c r="F350">
+        <v>1</v>
+      </c>
+      <c r="G350">
+        <v>1</v>
+      </c>
+      <c r="H350">
+        <v>18</v>
+      </c>
+      <c r="I350">
+        <v>162072285</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>TCT_Pin khác</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
         <is>
           <t>HCM</t>
         </is>
       </c>
-      <c r="C349" t="inlineStr">
-        <is>
-          <t>Chưa map wms</t>
-        </is>
-      </c>
-      <c r="D349" t="inlineStr">
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>Chưa map wms</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
         <is>
           <t>Miss</t>
         </is>
       </c>
-      <c r="E349">
+      <c r="E351">
         <v>20</v>
       </c>
-      <c r="F349">
-        <v>1</v>
-      </c>
-      <c r="G349">
+      <c r="F351">
+        <v>1</v>
+      </c>
+      <c r="G351">
         <v>0</v>
       </c>
-      <c r="H349">
+      <c r="H351">
         <v>0</v>
       </c>
-      <c r="I349">
+      <c r="I351">
         <v>28000000</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>TCT_Pin khác</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>QNH</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>Chưa map wms</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>Miss</t>
+        </is>
+      </c>
+      <c r="E352">
+        <v>10</v>
+      </c>
+      <c r="F352">
+        <v>1</v>
+      </c>
+      <c r="G352">
+        <v>0</v>
+      </c>
+      <c r="H352">
+        <v>0</v>
+      </c>
+      <c r="I352">
+        <v>113461215</v>
       </c>
     </row>
   </sheetData>
